--- a/research/traditional_assets/database/data/japan/japan_cable_tv.xlsx
+++ b/research/traditional_assets/database/data/japan/japan_cable_tv.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07700645914344054</v>
+        <v>0.07680188636554332</v>
       </c>
       <c r="C2">
-        <v>1932.890453706801</v>
+        <v>1922.600410581403</v>
       </c>
       <c r="D2">
-        <v>1583.190453706801</v>
+        <v>1593.637484743439</v>
       </c>
       <c r="E2">
-        <v>-435.3074162036236</v>
+        <v>-414.5703420415874</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>20.73707416203624</v>
       </c>
       <c r="G2">
         <v>349.7</v>
@@ -1451,28 +1451,28 @@
         <v>333.379</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.043074830350423</v>
       </c>
       <c r="N2">
-        <v>333.379</v>
+        <v>332.3359251696496</v>
       </c>
       <c r="O2">
-        <v>102.0806498</v>
+        <v>101.7612602869467</v>
       </c>
       <c r="P2">
-        <v>231.2983502</v>
+        <v>230.5746648827028</v>
       </c>
       <c r="Q2">
-        <v>231.6293501999999</v>
+        <v>230.9056648827028</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07700645914344054</v>
+        <v>0.07722515653085184</v>
       </c>
       <c r="T2">
-        <v>0.591974998450994</v>
+        <v>0.596123607076502</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>319.6117769307124</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07680188636554332</v>
+        <v>0.0765973135876461</v>
       </c>
       <c r="C3">
-        <v>1922.600410581403</v>
+        <v>1912.449157364018</v>
       </c>
       <c r="D3">
-        <v>1593.637484743439</v>
+        <v>1604.223305688091</v>
       </c>
       <c r="E3">
-        <v>-414.5703420415874</v>
+        <v>-393.8332678795512</v>
       </c>
       <c r="F3">
-        <v>20.73707416203624</v>
+        <v>41.47414832407247</v>
       </c>
       <c r="G3">
         <v>349.7</v>
@@ -1533,28 +1533,28 @@
         <v>333.379</v>
       </c>
       <c r="M3">
-        <v>1.043074830350423</v>
+        <v>2.086149660700845</v>
       </c>
       <c r="N3">
-        <v>332.3359251696496</v>
+        <v>331.2928503392991</v>
       </c>
       <c r="O3">
-        <v>101.7612602869467</v>
+        <v>101.4418707738934</v>
       </c>
       <c r="P3">
-        <v>230.5746648827028</v>
+        <v>229.8509795654057</v>
       </c>
       <c r="Q3">
-        <v>230.9056648827028</v>
+        <v>230.1819795654057</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07722515653085184</v>
+        <v>0.07744831713025113</v>
       </c>
       <c r="T3">
-        <v>0.596123607076502</v>
+        <v>0.6003568811841633</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>319.6117769307124</v>
+        <v>159.8058884653562</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0765973135876461</v>
+        <v>0.07639274080974889</v>
       </c>
       <c r="C4">
-        <v>1912.449157364018</v>
+        <v>1902.439478307015</v>
       </c>
       <c r="D4">
-        <v>1604.223305688091</v>
+        <v>1614.950700793124</v>
       </c>
       <c r="E4">
-        <v>-393.8332678795512</v>
+        <v>-373.0961937175149</v>
       </c>
       <c r="F4">
-        <v>41.47414832407247</v>
+        <v>62.21122248610871</v>
       </c>
       <c r="G4">
         <v>349.7</v>
@@ -1615,28 +1615,28 @@
         <v>333.379</v>
       </c>
       <c r="M4">
-        <v>2.086149660700845</v>
+        <v>3.129224491051268</v>
       </c>
       <c r="N4">
-        <v>331.2928503392991</v>
+        <v>330.2497755089487</v>
       </c>
       <c r="O4">
-        <v>101.4418707738934</v>
+        <v>101.1224812608401</v>
       </c>
       <c r="P4">
-        <v>229.8509795654057</v>
+        <v>229.1272942481086</v>
       </c>
       <c r="Q4">
-        <v>230.1819795654057</v>
+        <v>229.4582942481086</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07744831713025113</v>
+        <v>0.07767607897912257</v>
       </c>
       <c r="T4">
-        <v>0.6003568811841633</v>
+        <v>0.6046774392940446</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>159.8058884653562</v>
+        <v>106.5372589769041</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07639274080974889</v>
+        <v>0.07618816803185167</v>
       </c>
       <c r="C5">
-        <v>1902.439478307015</v>
+        <v>1892.574232636977</v>
       </c>
       <c r="D5">
-        <v>1614.950700793124</v>
+        <v>1625.822529285122</v>
       </c>
       <c r="E5">
-        <v>-373.0961937175149</v>
+        <v>-352.3591195554787</v>
       </c>
       <c r="F5">
-        <v>62.21122248610871</v>
+        <v>82.94829664814495</v>
       </c>
       <c r="G5">
         <v>349.7</v>
@@ -1697,28 +1697,28 @@
         <v>333.379</v>
       </c>
       <c r="M5">
-        <v>3.129224491051268</v>
+        <v>4.172299321401691</v>
       </c>
       <c r="N5">
-        <v>330.2497755089487</v>
+        <v>329.2067006785983</v>
       </c>
       <c r="O5">
-        <v>101.1224812608401</v>
+        <v>100.8030917477868</v>
       </c>
       <c r="P5">
-        <v>229.1272942481086</v>
+        <v>228.4036089308115</v>
       </c>
       <c r="Q5">
-        <v>229.4582942481086</v>
+        <v>228.7346089308114</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07767607897912257</v>
+        <v>0.07790858586651217</v>
       </c>
       <c r="T5">
-        <v>0.6046774392940446</v>
+        <v>0.6090880090312148</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>106.5372589769041</v>
+        <v>79.9029442326781</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07618816803185167</v>
+        <v>0.07598359525395447</v>
       </c>
       <c r="C6">
-        <v>1892.574232636977</v>
+        <v>1882.856357095428</v>
       </c>
       <c r="D6">
-        <v>1625.822529285122</v>
+        <v>1636.841727905609</v>
       </c>
       <c r="E6">
-        <v>-352.3591195554787</v>
+        <v>-331.6220453934424</v>
       </c>
       <c r="F6">
-        <v>82.94829664814495</v>
+        <v>103.6853708101812</v>
       </c>
       <c r="G6">
         <v>349.7</v>
@@ -1779,28 +1779,28 @@
         <v>333.379</v>
       </c>
       <c r="M6">
-        <v>4.172299321401691</v>
+        <v>5.215374151752114</v>
       </c>
       <c r="N6">
-        <v>329.2067006785983</v>
+        <v>328.1636258482479</v>
       </c>
       <c r="O6">
-        <v>100.8030917477868</v>
+        <v>100.4837022347335</v>
       </c>
       <c r="P6">
-        <v>228.4036089308115</v>
+        <v>227.6799236135143</v>
       </c>
       <c r="Q6">
-        <v>228.7346089308114</v>
+        <v>228.0109236135143</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07790858586651217</v>
+        <v>0.07814598763574154</v>
       </c>
       <c r="T6">
-        <v>0.6090880090312148</v>
+        <v>0.613591432868115</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>79.9029442326781</v>
+        <v>63.92235538614248</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07598359525395447</v>
+        <v>0.07577902247605725</v>
       </c>
       <c r="C7">
-        <v>1882.856357095428</v>
+        <v>1873.288868583597</v>
       </c>
       <c r="D7">
-        <v>1636.841727905609</v>
+        <v>1648.011313555814</v>
       </c>
       <c r="E7">
-        <v>-331.6220453934424</v>
+        <v>-310.8849712314062</v>
       </c>
       <c r="F7">
-        <v>103.6853708101812</v>
+        <v>124.4224449722174</v>
       </c>
       <c r="G7">
         <v>349.7</v>
@@ -1861,28 +1861,28 @@
         <v>333.379</v>
       </c>
       <c r="M7">
-        <v>5.215374151752114</v>
+        <v>6.258448982102537</v>
       </c>
       <c r="N7">
-        <v>328.1636258482479</v>
+        <v>327.1205510178974</v>
       </c>
       <c r="O7">
-        <v>100.4837022347335</v>
+        <v>100.1643127216802</v>
       </c>
       <c r="P7">
-        <v>227.6799236135143</v>
+        <v>226.9562382962172</v>
       </c>
       <c r="Q7">
-        <v>228.0109236135143</v>
+        <v>227.2872382962172</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07814598763574154</v>
+        <v>0.07838844050644389</v>
       </c>
       <c r="T7">
-        <v>0.613591432868115</v>
+        <v>0.61819067423346</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>63.92235538614248</v>
+        <v>53.26862948845206</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07577902247605725</v>
+        <v>0.07557444969816003</v>
       </c>
       <c r="C8">
-        <v>1873.288868583597</v>
+        <v>1863.874866916196</v>
       </c>
       <c r="D8">
-        <v>1648.011313555814</v>
+        <v>1659.33438605045</v>
       </c>
       <c r="E8">
-        <v>-310.8849712314062</v>
+        <v>-290.1478970693699</v>
       </c>
       <c r="F8">
-        <v>124.4224449722174</v>
+        <v>145.1595191342537</v>
       </c>
       <c r="G8">
         <v>349.7</v>
@@ -1943,28 +1943,28 @@
         <v>333.379</v>
       </c>
       <c r="M8">
-        <v>6.258448982102536</v>
+        <v>7.301523812452959</v>
       </c>
       <c r="N8">
-        <v>327.1205510178974</v>
+        <v>326.077476187547</v>
       </c>
       <c r="O8">
-        <v>100.1643127216802</v>
+        <v>99.84492320862691</v>
       </c>
       <c r="P8">
-        <v>226.9562382962172</v>
+        <v>226.2325529789201</v>
       </c>
       <c r="Q8">
-        <v>227.2872382962172</v>
+        <v>226.5635529789201</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07838844050644389</v>
+        <v>0.07863610741737638</v>
       </c>
       <c r="T8">
-        <v>0.61819067423346</v>
+        <v>0.6228888240152639</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>53.26862948845206</v>
+        <v>45.65882527581606</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07557444969816003</v>
+        <v>0.07536987692026283</v>
       </c>
       <c r="C9">
-        <v>1863.874866916196</v>
+        <v>1854.617537689523</v>
       </c>
       <c r="D9">
-        <v>1659.33438605045</v>
+        <v>1670.814130985813</v>
       </c>
       <c r="E9">
-        <v>-290.1478970693699</v>
+        <v>-269.4108229073337</v>
       </c>
       <c r="F9">
-        <v>145.1595191342537</v>
+        <v>165.8965932962899</v>
       </c>
       <c r="G9">
         <v>349.7</v>
@@ -2025,28 +2025,28 @@
         <v>333.379</v>
       </c>
       <c r="M9">
-        <v>7.30152381245296</v>
+        <v>8.344598642803382</v>
       </c>
       <c r="N9">
-        <v>326.077476187547</v>
+        <v>325.0344013571966</v>
       </c>
       <c r="O9">
-        <v>99.84492320862691</v>
+        <v>99.52553369557361</v>
       </c>
       <c r="P9">
-        <v>226.2325529789201</v>
+        <v>225.508867661623</v>
       </c>
       <c r="Q9">
-        <v>226.5635529789201</v>
+        <v>225.839867661623</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07863610741737638</v>
+        <v>0.07888915839159003</v>
       </c>
       <c r="T9">
-        <v>0.6228888240152639</v>
+        <v>0.6276891074879765</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>45.65882527581605</v>
+        <v>39.95147211633905</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07536987692026283</v>
+        <v>0.07516530414236561</v>
       </c>
       <c r="C10">
-        <v>1854.617537689523</v>
+        <v>1845.520155269435</v>
       </c>
       <c r="D10">
-        <v>1670.814130985813</v>
+        <v>1682.453822727761</v>
       </c>
       <c r="E10">
-        <v>-269.4108229073337</v>
+        <v>-248.6737487452975</v>
       </c>
       <c r="F10">
-        <v>165.8965932962899</v>
+        <v>186.6336674583261</v>
       </c>
       <c r="G10">
         <v>349.7</v>
@@ -2107,28 +2107,28 @@
         <v>333.379</v>
       </c>
       <c r="M10">
-        <v>8.344598642803382</v>
+        <v>9.387673473153804</v>
       </c>
       <c r="N10">
-        <v>325.0344013571966</v>
+        <v>323.9913265268461</v>
       </c>
       <c r="O10">
-        <v>99.52553369557361</v>
+        <v>99.20614418252029</v>
       </c>
       <c r="P10">
-        <v>225.508867661623</v>
+        <v>224.7851823443258</v>
       </c>
       <c r="Q10">
-        <v>225.839867661623</v>
+        <v>225.1161823443258</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07888915839159003</v>
+        <v>0.07914777092567649</v>
       </c>
       <c r="T10">
-        <v>0.6276891074879765</v>
+        <v>0.6325948916963532</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>39.95147211633905</v>
+        <v>35.51241965896804</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07516530414236561</v>
+        <v>0.07496073136446839</v>
       </c>
       <c r="C11">
-        <v>1845.520155269435</v>
+        <v>1836.586085905097</v>
       </c>
       <c r="D11">
-        <v>1682.453822727761</v>
+        <v>1694.25682752546</v>
       </c>
       <c r="E11">
-        <v>-248.6737487452975</v>
+        <v>-227.9366745832613</v>
       </c>
       <c r="F11">
-        <v>186.6336674583261</v>
+        <v>207.3707416203624</v>
       </c>
       <c r="G11">
         <v>349.7</v>
@@ -2189,28 +2189,28 @@
         <v>333.379</v>
       </c>
       <c r="M11">
-        <v>9.387673473153804</v>
+        <v>10.43074830350423</v>
       </c>
       <c r="N11">
-        <v>323.9913265268461</v>
+        <v>322.9482516964957</v>
       </c>
       <c r="O11">
-        <v>99.20614418252029</v>
+        <v>98.886754669467</v>
       </c>
       <c r="P11">
-        <v>224.7851823443258</v>
+        <v>224.0614970270287</v>
       </c>
       <c r="Q11">
-        <v>225.1161823443258</v>
+        <v>224.3924970270287</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07914777092567649</v>
+        <v>0.07941213040496488</v>
       </c>
       <c r="T11">
-        <v>0.6325948916963532</v>
+        <v>0.6376096933315829</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>35.51241965896804</v>
+        <v>31.96117769307124</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07496073136446839</v>
+        <v>0.07475615858657117</v>
       </c>
       <c r="C12">
-        <v>1836.586085905097</v>
+        <v>1827.818790974722</v>
       </c>
       <c r="D12">
-        <v>1694.25682752546</v>
+        <v>1706.22660675712</v>
       </c>
       <c r="E12">
-        <v>-227.9366745832612</v>
+        <v>-207.199600421225</v>
       </c>
       <c r="F12">
-        <v>207.3707416203624</v>
+        <v>228.1078157823986</v>
       </c>
       <c r="G12">
         <v>349.7</v>
@@ -2271,28 +2271,28 @@
         <v>333.379</v>
       </c>
       <c r="M12">
-        <v>10.43074830350423</v>
+        <v>11.47382313385465</v>
       </c>
       <c r="N12">
-        <v>322.9482516964957</v>
+        <v>321.9051768661453</v>
       </c>
       <c r="O12">
-        <v>98.886754669467</v>
+        <v>98.56736515641371</v>
       </c>
       <c r="P12">
-        <v>224.0614970270287</v>
+        <v>223.3378117097316</v>
       </c>
       <c r="Q12">
-        <v>224.3924970270287</v>
+        <v>223.6688117097316</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07941213040496488</v>
+        <v>0.07968243054670918</v>
       </c>
       <c r="T12">
-        <v>0.6376096933315829</v>
+        <v>0.6427371871383906</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>31.96117769307124</v>
+        <v>29.05561608461022</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07475615858657117</v>
+        <v>0.07455158580867395</v>
       </c>
       <c r="C13">
-        <v>1827.818790974722</v>
+        <v>1819.221830369871</v>
       </c>
       <c r="D13">
-        <v>1706.22660675712</v>
+        <v>1718.366720314305</v>
       </c>
       <c r="E13">
-        <v>-207.199600421225</v>
+        <v>-186.4625262591888</v>
       </c>
       <c r="F13">
-        <v>228.1078157823986</v>
+        <v>248.8448899444348</v>
       </c>
       <c r="G13">
         <v>349.7</v>
@@ -2353,28 +2353,28 @@
         <v>333.379</v>
       </c>
       <c r="M13">
-        <v>11.47382313385465</v>
+        <v>12.51689796420507</v>
       </c>
       <c r="N13">
-        <v>321.9051768661453</v>
+        <v>320.8621020357949</v>
       </c>
       <c r="O13">
-        <v>98.56736515641371</v>
+        <v>98.24797564336042</v>
       </c>
       <c r="P13">
-        <v>223.3378117097316</v>
+        <v>222.6141263924345</v>
       </c>
       <c r="Q13">
-        <v>223.6688117097316</v>
+        <v>222.9451263924345</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07968243054670918</v>
+        <v>0.07995887387349312</v>
       </c>
       <c r="T13">
-        <v>0.6427371871383906</v>
+        <v>0.647981214895353</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>29.05561608461022</v>
+        <v>26.63431474422604</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07455158580867395</v>
+        <v>0.07434701303077676</v>
       </c>
       <c r="C14">
-        <v>1819.221830369871</v>
+        <v>1810.798866025271</v>
       </c>
       <c r="D14">
-        <v>1718.366720314305</v>
+        <v>1730.680830131742</v>
       </c>
       <c r="E14">
-        <v>-186.4625262591888</v>
+        <v>-165.7254520971525</v>
       </c>
       <c r="F14">
-        <v>248.8448899444348</v>
+        <v>269.5819641064711</v>
       </c>
       <c r="G14">
         <v>349.7</v>
@@ -2435,28 +2435,28 @@
         <v>333.379</v>
       </c>
       <c r="M14">
-        <v>12.51689796420507</v>
+        <v>13.5599727945555</v>
       </c>
       <c r="N14">
-        <v>320.8621020357949</v>
+        <v>319.8190272054445</v>
       </c>
       <c r="O14">
-        <v>98.24797564336042</v>
+        <v>97.9285861303071</v>
       </c>
       <c r="P14">
-        <v>222.6141263924345</v>
+        <v>221.8904410751373</v>
       </c>
       <c r="Q14">
-        <v>222.9451263924345</v>
+        <v>222.2214410751373</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07995887387349312</v>
+        <v>0.08024167221928362</v>
       </c>
       <c r="T14">
-        <v>0.647981214895353</v>
+        <v>0.6533457950145446</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>26.63431474422604</v>
+        <v>24.58552130236249</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07434701303077676</v>
+        <v>0.07414244025287953</v>
       </c>
       <c r="C15">
-        <v>1810.798866025271</v>
+        <v>1802.553665601508</v>
       </c>
       <c r="D15">
-        <v>1730.680830131742</v>
+        <v>1743.172703870016</v>
       </c>
       <c r="E15">
-        <v>-165.7254520971525</v>
+        <v>-144.9883779351163</v>
       </c>
       <c r="F15">
-        <v>269.5819641064711</v>
+        <v>290.3190382685074</v>
       </c>
       <c r="G15">
         <v>349.7</v>
@@ -2517,28 +2517,28 @@
         <v>333.379</v>
       </c>
       <c r="M15">
-        <v>13.5599727945555</v>
+        <v>14.60304762490592</v>
       </c>
       <c r="N15">
-        <v>319.8190272054445</v>
+        <v>318.7759523750941</v>
       </c>
       <c r="O15">
-        <v>97.9285861303071</v>
+        <v>97.6091966172538</v>
       </c>
       <c r="P15">
-        <v>221.8904410751373</v>
+        <v>221.1667557578402</v>
       </c>
       <c r="Q15">
-        <v>222.2214410751373</v>
+        <v>221.4977557578402</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08024167221928362</v>
+        <v>0.08053104727079016</v>
       </c>
       <c r="T15">
-        <v>0.6533457950145446</v>
+        <v>0.6588351328109265</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>24.58552130236249</v>
+        <v>22.82941263790802</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07414244025287953</v>
+        <v>0.07393786747498231</v>
       </c>
       <c r="C16">
-        <v>1802.553665601508</v>
+        <v>1794.490106328344</v>
       </c>
       <c r="D16">
-        <v>1743.172703870016</v>
+        <v>1755.846218758888</v>
       </c>
       <c r="E16">
-        <v>-144.9883779351163</v>
+        <v>-124.25130377308</v>
       </c>
       <c r="F16">
-        <v>290.3190382685074</v>
+        <v>311.0561124305436</v>
       </c>
       <c r="G16">
         <v>349.7</v>
@@ -2599,28 +2599,28 @@
         <v>333.379</v>
       </c>
       <c r="M16">
-        <v>14.60304762490592</v>
+        <v>15.64612245525634</v>
       </c>
       <c r="N16">
-        <v>318.7759523750941</v>
+        <v>317.7328775447436</v>
       </c>
       <c r="O16">
-        <v>97.6091966172538</v>
+        <v>97.28980710420051</v>
       </c>
       <c r="P16">
-        <v>221.1667557578402</v>
+        <v>220.4430704405431</v>
       </c>
       <c r="Q16">
-        <v>221.4977557578402</v>
+        <v>220.7740704405431</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08053104727079016</v>
+        <v>0.08082723114703802</v>
       </c>
       <c r="T16">
-        <v>0.6588351328109265</v>
+        <v>0.6644536314966351</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>22.82941263790802</v>
+        <v>21.30745179538082</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07393786747498231</v>
+        <v>0.0737332946970851</v>
       </c>
       <c r="C17">
-        <v>1794.490106328344</v>
+        <v>1786.61217901694</v>
       </c>
       <c r="D17">
-        <v>1755.846218758888</v>
+        <v>1768.70536560952</v>
       </c>
       <c r="E17">
-        <v>-124.2513037730801</v>
+        <v>-103.5142296110438</v>
       </c>
       <c r="F17">
-        <v>311.0561124305436</v>
+        <v>331.7931865925798</v>
       </c>
       <c r="G17">
         <v>349.7</v>
@@ -2681,28 +2681,28 @@
         <v>333.379</v>
       </c>
       <c r="M17">
-        <v>15.64612245525634</v>
+        <v>16.68919728560676</v>
       </c>
       <c r="N17">
-        <v>317.7328775447436</v>
+        <v>316.6898027143932</v>
       </c>
       <c r="O17">
-        <v>97.28980710420051</v>
+        <v>96.9704175911472</v>
       </c>
       <c r="P17">
-        <v>220.4430704405431</v>
+        <v>219.719385123246</v>
       </c>
       <c r="Q17">
-        <v>220.7740704405431</v>
+        <v>220.050385123246</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08082723114703802</v>
+        <v>0.08113046702033941</v>
       </c>
       <c r="T17">
-        <v>0.6644536314966351</v>
+        <v>0.6702059039605749</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>21.30745179538082</v>
+        <v>19.97573605816952</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0737332946970851</v>
+        <v>0.07352872191918788</v>
       </c>
       <c r="C18">
-        <v>1786.61217901694</v>
+        <v>1778.923992249677</v>
       </c>
       <c r="D18">
-        <v>1768.70536560952</v>
+        <v>1781.754253004293</v>
       </c>
       <c r="E18">
-        <v>-103.5142296110438</v>
+        <v>-82.77715544900758</v>
       </c>
       <c r="F18">
-        <v>331.7931865925798</v>
+        <v>352.5302607546161</v>
       </c>
       <c r="G18">
         <v>349.7</v>
@@ -2763,28 +2763,28 @@
         <v>333.379</v>
       </c>
       <c r="M18">
-        <v>16.68919728560676</v>
+        <v>17.73227211595719</v>
       </c>
       <c r="N18">
-        <v>316.6898027143932</v>
+        <v>315.6467278840428</v>
       </c>
       <c r="O18">
-        <v>96.9704175911472</v>
+        <v>96.6510280780939</v>
       </c>
       <c r="P18">
-        <v>219.719385123246</v>
+        <v>218.9956998059489</v>
       </c>
       <c r="Q18">
-        <v>220.050385123246</v>
+        <v>219.3266998059489</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08113046702033941</v>
+        <v>0.08144100978215407</v>
       </c>
       <c r="T18">
-        <v>0.6702059039605749</v>
+        <v>0.6760967853995493</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>19.97573605816952</v>
+        <v>18.80069276063014</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07352872191918788</v>
+        <v>0.07332414914129066</v>
       </c>
       <c r="C19">
-        <v>1778.923992249677</v>
+        <v>1771.429776756811</v>
       </c>
       <c r="D19">
-        <v>1781.754253004293</v>
+        <v>1794.997111673463</v>
       </c>
       <c r="E19">
-        <v>-82.77715544900758</v>
+        <v>-62.04008128697131</v>
       </c>
       <c r="F19">
-        <v>352.5302607546161</v>
+        <v>373.2673349166523</v>
       </c>
       <c r="G19">
         <v>349.7</v>
@@ -2845,28 +2845,28 @@
         <v>333.379</v>
       </c>
       <c r="M19">
-        <v>17.73227211595719</v>
+        <v>18.77534694630761</v>
       </c>
       <c r="N19">
-        <v>315.6467278840428</v>
+        <v>314.6036530536924</v>
       </c>
       <c r="O19">
-        <v>96.6510280780939</v>
+        <v>96.33163856504061</v>
       </c>
       <c r="P19">
-        <v>218.9956998059489</v>
+        <v>218.2720144886518</v>
       </c>
       <c r="Q19">
-        <v>219.3266998059489</v>
+        <v>218.6030144886518</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08144100978215407</v>
+        <v>0.08175912675767155</v>
       </c>
       <c r="T19">
-        <v>0.6760967853995493</v>
+        <v>0.6821313468736208</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>18.80069276063014</v>
+        <v>17.75620982948402</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07332414914129068</v>
+        <v>0.07311957636339346</v>
       </c>
       <c r="C20">
-        <v>1771.42977675681</v>
+        <v>1764.133889989779</v>
       </c>
       <c r="D20">
-        <v>1794.997111673462</v>
+        <v>1808.438299068468</v>
       </c>
       <c r="E20">
-        <v>-62.04008128697137</v>
+        <v>-41.30300712493511</v>
       </c>
       <c r="F20">
-        <v>373.2673349166523</v>
+        <v>394.0044090786885</v>
       </c>
       <c r="G20">
         <v>349.7</v>
@@ -2927,28 +2927,28 @@
         <v>333.379</v>
       </c>
       <c r="M20">
-        <v>18.77534694630761</v>
+        <v>19.81842177665803</v>
       </c>
       <c r="N20">
-        <v>314.6036530536924</v>
+        <v>313.5605782233419</v>
       </c>
       <c r="O20">
-        <v>96.33163856504061</v>
+        <v>96.0122490519873</v>
       </c>
       <c r="P20">
-        <v>218.2720144886518</v>
+        <v>217.5483291713546</v>
       </c>
       <c r="Q20">
-        <v>218.6030144886518</v>
+        <v>217.8793291713546</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08175912675767155</v>
+        <v>0.08208509847332525</v>
       </c>
       <c r="T20">
-        <v>0.6821313468736206</v>
+        <v>0.6883149098655704</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>17.75620982948402</v>
+        <v>16.82167247003749</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07311957636339346</v>
+        <v>0.07291500358549624</v>
       </c>
       <c r="C21">
-        <v>1764.133889989779</v>
+        <v>1757.040820901525</v>
       </c>
       <c r="D21">
-        <v>1808.438299068468</v>
+        <v>1822.08230414225</v>
       </c>
       <c r="E21">
-        <v>-41.30300712493511</v>
+        <v>-20.56593296289884</v>
       </c>
       <c r="F21">
-        <v>394.0044090786885</v>
+        <v>414.7414832407248</v>
       </c>
       <c r="G21">
         <v>349.7</v>
@@ -3009,28 +3009,28 @@
         <v>333.379</v>
       </c>
       <c r="M21">
-        <v>19.81842177665803</v>
+        <v>20.86149660700845</v>
       </c>
       <c r="N21">
-        <v>313.5605782233419</v>
+        <v>312.5175033929915</v>
       </c>
       <c r="O21">
-        <v>96.0122490519873</v>
+        <v>95.692859538934</v>
       </c>
       <c r="P21">
-        <v>217.5483291713546</v>
+        <v>216.8246438540575</v>
       </c>
       <c r="Q21">
-        <v>217.8793291713546</v>
+        <v>217.1556438540575</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08208509847332525</v>
+        <v>0.0824192194818703</v>
       </c>
       <c r="T21">
-        <v>0.6883149098655704</v>
+        <v>0.6946530619323188</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>16.82167247003749</v>
+        <v>15.98058884653562</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07291500358549624</v>
+        <v>0.07271043080759904</v>
       </c>
       <c r="C22">
-        <v>1757.040820901525</v>
+        <v>1750.155194944862</v>
       </c>
       <c r="D22">
-        <v>1822.08230414225</v>
+        <v>1835.933752347623</v>
       </c>
       <c r="E22">
-        <v>-20.56593296289884</v>
+        <v>0.1711411991374234</v>
       </c>
       <c r="F22">
-        <v>414.7414832407248</v>
+        <v>435.4785574027611</v>
       </c>
       <c r="G22">
         <v>349.7</v>
@@ -3091,28 +3091,28 @@
         <v>333.379</v>
       </c>
       <c r="M22">
-        <v>20.86149660700845</v>
+        <v>21.90457143735888</v>
       </c>
       <c r="N22">
-        <v>312.5175033929915</v>
+        <v>311.4744285626411</v>
       </c>
       <c r="O22">
-        <v>95.692859538934</v>
+        <v>95.37347002588071</v>
       </c>
       <c r="P22">
-        <v>216.8246438540575</v>
+        <v>216.1009585367604</v>
       </c>
       <c r="Q22">
-        <v>217.1556438540575</v>
+        <v>216.4319585367604</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0824192194818703</v>
+        <v>0.08276179925012535</v>
       </c>
       <c r="T22">
-        <v>0.6946530619323188</v>
+        <v>0.7011516735450609</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.98058884653562</v>
+        <v>15.21960842527202</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07271043080759904</v>
+        <v>0.07250585802970182</v>
       </c>
       <c r="C23">
-        <v>1750.155194944862</v>
+        <v>1743.481779300568</v>
       </c>
       <c r="D23">
-        <v>1835.933752347623</v>
+        <v>1849.997410865365</v>
       </c>
       <c r="E23">
-        <v>0.1711411991373666</v>
+        <v>20.90821536117357</v>
       </c>
       <c r="F23">
-        <v>435.478557402761</v>
+        <v>456.2156315647972</v>
       </c>
       <c r="G23">
         <v>349.7</v>
@@ -3173,28 +3173,28 @@
         <v>333.379</v>
       </c>
       <c r="M23">
-        <v>21.90457143735888</v>
+        <v>22.9476462677093</v>
       </c>
       <c r="N23">
-        <v>311.4744285626411</v>
+        <v>310.4313537322907</v>
       </c>
       <c r="O23">
-        <v>95.37347002588071</v>
+        <v>95.05408051282741</v>
       </c>
       <c r="P23">
-        <v>216.1009585367604</v>
+        <v>215.3772732194633</v>
       </c>
       <c r="Q23">
-        <v>216.4319585367604</v>
+        <v>215.7082732194633</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08276179925012535</v>
+        <v>0.08311316311500233</v>
       </c>
       <c r="T23">
-        <v>0.7011516735450609</v>
+        <v>0.7078169162247965</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.21960842527202</v>
+        <v>14.52780804230511</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07250585802970182</v>
+        <v>0.0723012852518046</v>
       </c>
       <c r="C24">
-        <v>1743.481779300568</v>
+        <v>1737.025488347626</v>
       </c>
       <c r="D24">
-        <v>1849.997410865365</v>
+        <v>1864.278194074459</v>
       </c>
       <c r="E24">
-        <v>20.90821536117357</v>
+        <v>41.64528952320984</v>
       </c>
       <c r="F24">
-        <v>456.2156315647972</v>
+        <v>476.9527057268335</v>
       </c>
       <c r="G24">
         <v>349.7</v>
@@ -3255,28 +3255,28 @@
         <v>333.379</v>
       </c>
       <c r="M24">
-        <v>22.9476462677093</v>
+        <v>23.99072109805972</v>
       </c>
       <c r="N24">
-        <v>310.4313537322907</v>
+        <v>309.3882789019402</v>
       </c>
       <c r="O24">
-        <v>95.05408051282741</v>
+        <v>94.7346909997741</v>
       </c>
       <c r="P24">
-        <v>215.3772732194633</v>
+        <v>214.6535879021661</v>
       </c>
       <c r="Q24">
-        <v>215.7082732194633</v>
+        <v>214.9845879021661</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08311316311500233</v>
+        <v>0.08347365331403195</v>
       </c>
       <c r="T24">
-        <v>0.7078169162247965</v>
+        <v>0.7146552820910186</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.52780804230511</v>
+        <v>13.8961642143788</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0723012852518046</v>
+        <v>0.07209671247390738</v>
       </c>
       <c r="C25">
-        <v>1737.025488347626</v>
+        <v>1730.7913893888</v>
       </c>
       <c r="D25">
-        <v>1864.278194074459</v>
+        <v>1878.781169277669</v>
       </c>
       <c r="E25">
-        <v>41.64528952320984</v>
+        <v>62.3823636852461</v>
       </c>
       <c r="F25">
-        <v>476.9527057268335</v>
+        <v>497.6897798888697</v>
       </c>
       <c r="G25">
         <v>349.7</v>
@@ -3337,28 +3337,28 @@
         <v>333.379</v>
       </c>
       <c r="M25">
-        <v>23.99072109805972</v>
+        <v>25.03379592841015</v>
       </c>
       <c r="N25">
-        <v>309.3882789019402</v>
+        <v>308.3452040715898</v>
       </c>
       <c r="O25">
-        <v>94.7346909997741</v>
+        <v>94.41530148672081</v>
       </c>
       <c r="P25">
-        <v>214.6535879021661</v>
+        <v>213.929902584869</v>
       </c>
       <c r="Q25">
-        <v>214.9845879021661</v>
+        <v>214.260902584869</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08347365331403195</v>
+        <v>0.08384363009724655</v>
       </c>
       <c r="T25">
-        <v>0.7146552820910186</v>
+        <v>0.7216736049537201</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>13.8961642143788</v>
+        <v>13.31715737211302</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07209671247390738</v>
+        <v>0.07215231469601016</v>
       </c>
       <c r="C26">
-        <v>1730.7913893888</v>
+        <v>1706.090169797348</v>
       </c>
       <c r="D26">
-        <v>1878.781169277669</v>
+        <v>1874.817023848254</v>
       </c>
       <c r="E26">
-        <v>62.38236368524605</v>
+        <v>83.11943784728231</v>
       </c>
       <c r="F26">
-        <v>497.6897798888697</v>
+        <v>518.4268540509059</v>
       </c>
       <c r="G26">
         <v>349.7</v>
@@ -3419,45 +3419,45 @@
         <v>333.379</v>
       </c>
       <c r="M26">
-        <v>25.03379592841014</v>
+        <v>26.85451103983693</v>
       </c>
       <c r="N26">
-        <v>308.3452040715898</v>
+        <v>306.524488960163</v>
       </c>
       <c r="O26">
-        <v>94.41530148672081</v>
+        <v>93.85779851960193</v>
       </c>
       <c r="P26">
-        <v>213.929902584869</v>
+        <v>212.6666904405611</v>
       </c>
       <c r="Q26">
-        <v>214.260902584869</v>
+        <v>212.9976904405611</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08384363009724655</v>
+        <v>0.08422347292801355</v>
       </c>
       <c r="T26">
-        <v>0.7216736049537201</v>
+        <v>0.7288790830927606</v>
       </c>
       <c r="U26">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V26">
         <v>0.3062</v>
       </c>
       <c r="W26">
-        <v>0.03489813999999999</v>
+        <v>0.03593884</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y26">
-        <v>13.31715737211302</v>
+        <v>12.41426438580296</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07215231469601016</v>
+        <v>0.07195814891811296</v>
       </c>
       <c r="C27">
-        <v>1706.090169797348</v>
+        <v>1699.26942079234</v>
       </c>
       <c r="D27">
-        <v>1874.817023848254</v>
+        <v>1888.733349005282</v>
       </c>
       <c r="E27">
-        <v>83.11943784728231</v>
+        <v>103.8565120093186</v>
       </c>
       <c r="F27">
-        <v>518.4268540509059</v>
+        <v>539.1639282129422</v>
       </c>
       <c r="G27">
         <v>349.7</v>
@@ -3501,28 +3501,28 @@
         <v>333.379</v>
       </c>
       <c r="M27">
-        <v>26.85451103983693</v>
+        <v>27.92869148143041</v>
       </c>
       <c r="N27">
-        <v>306.524488960163</v>
+        <v>305.4503085185696</v>
       </c>
       <c r="O27">
-        <v>93.85779851960193</v>
+        <v>93.52888446838601</v>
       </c>
       <c r="P27">
-        <v>212.6666904405611</v>
+        <v>211.9214240501835</v>
       </c>
       <c r="Q27">
-        <v>212.9976904405611</v>
+        <v>212.2524240501835</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08422347292801355</v>
+        <v>0.08461358178123372</v>
       </c>
       <c r="T27">
-        <v>0.7288790830927606</v>
+        <v>0.7362793038842075</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>12.41426438580296</v>
+        <v>11.93679267865669</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07195814891811296</v>
+        <v>0.07176398314021573</v>
       </c>
       <c r="C28">
-        <v>1699.26942079234</v>
+        <v>1692.656811970216</v>
       </c>
       <c r="D28">
-        <v>1888.733349005282</v>
+        <v>1902.857814345194</v>
       </c>
       <c r="E28">
-        <v>103.8565120093186</v>
+        <v>124.5935861713548</v>
       </c>
       <c r="F28">
-        <v>539.1639282129422</v>
+        <v>559.9010023749785</v>
       </c>
       <c r="G28">
         <v>349.7</v>
@@ -3583,28 +3583,28 @@
         <v>333.379</v>
       </c>
       <c r="M28">
-        <v>27.92869148143041</v>
+        <v>29.00287192302389</v>
       </c>
       <c r="N28">
-        <v>305.4503085185696</v>
+        <v>304.3761280769761</v>
       </c>
       <c r="O28">
-        <v>93.52888446838601</v>
+        <v>93.19997041717009</v>
       </c>
       <c r="P28">
-        <v>211.9214240501835</v>
+        <v>211.176157659806</v>
       </c>
       <c r="Q28">
-        <v>212.2524240501835</v>
+        <v>211.507157659806</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08461358178123372</v>
+        <v>0.08501437854824073</v>
       </c>
       <c r="T28">
-        <v>0.7362793038842075</v>
+        <v>0.7438822704507624</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.93679267865669</v>
+        <v>11.49468924611385</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07176398314021573</v>
+        <v>0.07156981736231852</v>
       </c>
       <c r="C29">
-        <v>1692.656811970216</v>
+        <v>1686.257048102446</v>
       </c>
       <c r="D29">
-        <v>1902.857814345194</v>
+        <v>1917.195124639461</v>
       </c>
       <c r="E29">
-        <v>124.5935861713548</v>
+        <v>145.3306603333911</v>
       </c>
       <c r="F29">
-        <v>559.9010023749785</v>
+        <v>580.6380765370147</v>
       </c>
       <c r="G29">
         <v>349.7</v>
@@ -3665,28 +3665,28 @@
         <v>333.379</v>
       </c>
       <c r="M29">
-        <v>29.00287192302389</v>
+        <v>30.07705236461736</v>
       </c>
       <c r="N29">
-        <v>304.3761280769761</v>
+        <v>303.3019476353826</v>
       </c>
       <c r="O29">
-        <v>93.19997041717009</v>
+        <v>92.87105636595416</v>
       </c>
       <c r="P29">
-        <v>211.176157659806</v>
+        <v>210.4308912694284</v>
       </c>
       <c r="Q29">
-        <v>211.507157659806</v>
+        <v>210.7618912694284</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08501437854824073</v>
+        <v>0.08542630855877573</v>
       </c>
       <c r="T29">
-        <v>0.7438822704507624</v>
+        <v>0.751696430533055</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.49468924611385</v>
+        <v>11.08416463018121</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07156981736231852</v>
+        <v>0.07137565158442129</v>
       </c>
       <c r="C30">
-        <v>1686.257048102446</v>
+        <v>1680.074976831641</v>
       </c>
       <c r="D30">
-        <v>1917.195124639461</v>
+        <v>1931.750127530692</v>
       </c>
       <c r="E30">
-        <v>145.3306603333911</v>
+        <v>166.0677344954274</v>
       </c>
       <c r="F30">
-        <v>580.6380765370147</v>
+        <v>601.375150699051</v>
       </c>
       <c r="G30">
         <v>349.7</v>
@@ -3747,28 +3747,28 @@
         <v>333.379</v>
       </c>
       <c r="M30">
-        <v>30.07705236461736</v>
+        <v>31.15123280621084</v>
       </c>
       <c r="N30">
-        <v>303.3019476353826</v>
+        <v>302.2277671937891</v>
       </c>
       <c r="O30">
-        <v>92.87105636595416</v>
+        <v>92.54214231473824</v>
       </c>
       <c r="P30">
-        <v>210.4308912694284</v>
+        <v>209.6856248790509</v>
       </c>
       <c r="Q30">
-        <v>210.7618912694284</v>
+        <v>210.0166248790509</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08542630855877573</v>
+        <v>0.08584984223157929</v>
       </c>
       <c r="T30">
-        <v>0.751696430533055</v>
+        <v>0.7597307078007642</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.08416463018121</v>
+        <v>10.70195205672669</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07137565158442129</v>
+        <v>0.07118148580652409</v>
       </c>
       <c r="C31">
-        <v>1680.074976831642</v>
+        <v>1674.115594136296</v>
       </c>
       <c r="D31">
-        <v>1931.750127530692</v>
+        <v>1946.527818997384</v>
       </c>
       <c r="E31">
-        <v>166.0677344954273</v>
+        <v>186.8048086574635</v>
       </c>
       <c r="F31">
-        <v>601.3751506990509</v>
+        <v>622.1122248610872</v>
       </c>
       <c r="G31">
         <v>349.7</v>
@@ -3829,28 +3829,28 @@
         <v>333.379</v>
       </c>
       <c r="M31">
-        <v>31.15123280621084</v>
+        <v>32.22541324780431</v>
       </c>
       <c r="N31">
-        <v>302.2277671937891</v>
+        <v>301.1535867521957</v>
       </c>
       <c r="O31">
-        <v>92.54214231473824</v>
+        <v>92.21322826352232</v>
       </c>
       <c r="P31">
-        <v>209.6856248790509</v>
+        <v>208.9403584886734</v>
       </c>
       <c r="Q31">
-        <v>210.0166248790509</v>
+        <v>209.2713584886733</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08584984223157929</v>
+        <v>0.08628547686646298</v>
       </c>
       <c r="T31">
-        <v>0.7597307078007642</v>
+        <v>0.767994535847551</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.70195205672669</v>
+        <v>10.34522032150247</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07118148580652409</v>
+        <v>0.07098732002862687</v>
       </c>
       <c r="C32">
-        <v>1674.115594136296</v>
+        <v>1668.384050048307</v>
       </c>
       <c r="D32">
-        <v>1946.527818997384</v>
+        <v>1961.53334907143</v>
       </c>
       <c r="E32">
-        <v>186.8048086574635</v>
+        <v>207.5418828194998</v>
       </c>
       <c r="F32">
-        <v>622.1122248610872</v>
+        <v>642.8492990231234</v>
       </c>
       <c r="G32">
         <v>349.7</v>
@@ -3911,28 +3911,28 @@
         <v>333.379</v>
       </c>
       <c r="M32">
-        <v>32.22541324780431</v>
+        <v>33.2995936893978</v>
       </c>
       <c r="N32">
-        <v>301.1535867521957</v>
+        <v>300.0794063106022</v>
       </c>
       <c r="O32">
-        <v>92.21322826352232</v>
+        <v>91.88431421230639</v>
       </c>
       <c r="P32">
-        <v>208.9403584886734</v>
+        <v>208.1950920982958</v>
       </c>
       <c r="Q32">
-        <v>209.2713584886733</v>
+        <v>208.5260920982958</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08628547686646298</v>
+        <v>0.08673373859221287</v>
       </c>
       <c r="T32">
-        <v>0.767994535847551</v>
+        <v>0.7764978951420707</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.34522032150247</v>
+        <v>10.01150353693787</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07098732002862687</v>
+        <v>0.07117058145072966</v>
       </c>
       <c r="C33">
-        <v>1668.384050048307</v>
+        <v>1633.478069598057</v>
       </c>
       <c r="D33">
-        <v>1961.53334907143</v>
+        <v>1947.364442783217</v>
       </c>
       <c r="E33">
-        <v>207.5418828194998</v>
+        <v>228.2789569815359</v>
       </c>
       <c r="F33">
-        <v>642.8492990231234</v>
+        <v>663.5863731851596</v>
       </c>
       <c r="G33">
         <v>349.7</v>
@@ -3993,45 +3993,45 @@
         <v>333.379</v>
       </c>
       <c r="M33">
-        <v>33.2995936893978</v>
+        <v>35.50187096540603</v>
       </c>
       <c r="N33">
-        <v>300.0794063106022</v>
+        <v>297.8771290345939</v>
       </c>
       <c r="O33">
-        <v>91.88431421230639</v>
+        <v>91.20997691039267</v>
       </c>
       <c r="P33">
-        <v>208.1950920982958</v>
+        <v>206.6671521242012</v>
       </c>
       <c r="Q33">
-        <v>208.5260920982958</v>
+        <v>206.9981521242012</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08673373859221287</v>
+        <v>0.08719518448636715</v>
       </c>
       <c r="T33">
-        <v>0.7764978951420707</v>
+        <v>0.7852513532393703</v>
       </c>
       <c r="U33">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V33">
         <v>0.3062</v>
       </c>
       <c r="W33">
-        <v>0.03593884</v>
+        <v>0.0371183</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>10.01150353693787</v>
+        <v>9.390462838560065</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07117058145072966</v>
+        <v>0.07098821027283245</v>
       </c>
       <c r="C34">
-        <v>1633.478069598057</v>
+        <v>1626.840573904626</v>
       </c>
       <c r="D34">
-        <v>1947.364442783217</v>
+        <v>1961.464021251822</v>
       </c>
       <c r="E34">
-        <v>228.2789569815359</v>
+        <v>249.0160311435722</v>
       </c>
       <c r="F34">
-        <v>663.5863731851596</v>
+        <v>684.3234473471958</v>
       </c>
       <c r="G34">
         <v>349.7</v>
@@ -4075,28 +4075,28 @@
         <v>333.379</v>
       </c>
       <c r="M34">
-        <v>35.50187096540603</v>
+        <v>36.61130443307498</v>
       </c>
       <c r="N34">
-        <v>297.8771290345939</v>
+        <v>296.767695566925</v>
       </c>
       <c r="O34">
-        <v>91.20997691039267</v>
+        <v>90.87026838259244</v>
       </c>
       <c r="P34">
-        <v>206.6671521242012</v>
+        <v>205.8974271843326</v>
       </c>
       <c r="Q34">
-        <v>206.9981521242012</v>
+        <v>206.2284271843326</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08719518448636715</v>
+        <v>0.08767040488482455</v>
       </c>
       <c r="T34">
-        <v>0.7852513532393703</v>
+        <v>0.7942661085933058</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.390462838560065</v>
+        <v>9.105903358603701</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07098821027283245</v>
+        <v>0.07080583909493524</v>
       </c>
       <c r="C35">
-        <v>1626.840573904626</v>
+        <v>1620.408738715</v>
       </c>
       <c r="D35">
-        <v>1961.464021251822</v>
+        <v>1975.769260224232</v>
       </c>
       <c r="E35">
-        <v>249.0160311435722</v>
+        <v>269.7531053056085</v>
       </c>
       <c r="F35">
-        <v>684.3234473471958</v>
+        <v>705.0605215092321</v>
       </c>
       <c r="G35">
         <v>349.7</v>
@@ -4157,28 +4157,28 @@
         <v>333.379</v>
       </c>
       <c r="M35">
-        <v>36.61130443307498</v>
+        <v>37.72073790074392</v>
       </c>
       <c r="N35">
-        <v>296.767695566925</v>
+        <v>295.658262099256</v>
       </c>
       <c r="O35">
-        <v>90.87026838259244</v>
+        <v>90.5305598547922</v>
       </c>
       <c r="P35">
-        <v>205.8974271843326</v>
+        <v>205.1277022444638</v>
       </c>
       <c r="Q35">
-        <v>206.2284271843326</v>
+        <v>205.4587022444638</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08767040488482455</v>
+        <v>0.08816002590141703</v>
       </c>
       <c r="T35">
-        <v>0.7942661085933058</v>
+        <v>0.803554038351906</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>9.105903358603701</v>
+        <v>8.838082671585944</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07080583909493524</v>
+        <v>0.070623467917038</v>
       </c>
       <c r="C36">
-        <v>1620.408738715</v>
+        <v>1614.187096822318</v>
       </c>
       <c r="D36">
-        <v>1975.769260224232</v>
+        <v>1990.284692493587</v>
       </c>
       <c r="E36">
-        <v>269.7531053056085</v>
+        <v>290.4901794676447</v>
       </c>
       <c r="F36">
-        <v>705.0605215092321</v>
+        <v>725.7975956712684</v>
       </c>
       <c r="G36">
         <v>349.7</v>
@@ -4239,28 +4239,28 @@
         <v>333.379</v>
       </c>
       <c r="M36">
-        <v>37.72073790074392</v>
+        <v>38.83017136841286</v>
       </c>
       <c r="N36">
-        <v>295.658262099256</v>
+        <v>294.5488286315871</v>
       </c>
       <c r="O36">
-        <v>90.5305598547922</v>
+        <v>90.19085132699199</v>
       </c>
       <c r="P36">
-        <v>205.1277022444638</v>
+        <v>204.3579773045951</v>
       </c>
       <c r="Q36">
-        <v>205.4587022444638</v>
+        <v>204.6889773045951</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08816002590141703</v>
+        <v>0.08866471218005847</v>
       </c>
       <c r="T36">
-        <v>0.803554038351906</v>
+        <v>0.8131277505646168</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.838082671585944</v>
+        <v>8.585566023826345</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.070623467917038</v>
+        <v>0.07044109673914078</v>
       </c>
       <c r="C37">
-        <v>1614.187096822318</v>
+        <v>1608.1803152103</v>
       </c>
       <c r="D37">
-        <v>1990.284692493587</v>
+        <v>2005.014985043605</v>
       </c>
       <c r="E37">
-        <v>290.4901794676447</v>
+        <v>311.227253629681</v>
       </c>
       <c r="F37">
-        <v>725.7975956712684</v>
+        <v>746.5346698333046</v>
       </c>
       <c r="G37">
         <v>349.7</v>
@@ -4321,28 +4321,28 @@
         <v>333.379</v>
       </c>
       <c r="M37">
-        <v>38.83017136841286</v>
+        <v>39.9396048360818</v>
       </c>
       <c r="N37">
-        <v>294.5488286315871</v>
+        <v>293.4393951639182</v>
       </c>
       <c r="O37">
-        <v>90.19085132699199</v>
+        <v>89.85114279919175</v>
       </c>
       <c r="P37">
-        <v>204.3579773045951</v>
+        <v>203.5882523647264</v>
       </c>
       <c r="Q37">
-        <v>204.6889773045951</v>
+        <v>203.9192523647264</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08866471218005847</v>
+        <v>0.08918516990490749</v>
       </c>
       <c r="T37">
-        <v>0.8131277505646168</v>
+        <v>0.823000641283975</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.585566023826345</v>
+        <v>8.347078078720056</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0704410967391408</v>
+        <v>0.07025872556124359</v>
       </c>
       <c r="C38">
-        <v>1608.180315210299</v>
+        <v>1602.393200056077</v>
       </c>
       <c r="D38">
-        <v>2005.014985043604</v>
+        <v>2019.964944051417</v>
       </c>
       <c r="E38">
-        <v>311.2272536296809</v>
+        <v>331.9643277917172</v>
       </c>
       <c r="F38">
-        <v>746.5346698333045</v>
+        <v>767.2717439953408</v>
       </c>
       <c r="G38">
         <v>349.7</v>
@@ -4403,28 +4403,28 @@
         <v>333.379</v>
       </c>
       <c r="M38">
-        <v>39.93960483608179</v>
+        <v>41.04903830375073</v>
       </c>
       <c r="N38">
-        <v>293.4393951639182</v>
+        <v>292.3299616962493</v>
       </c>
       <c r="O38">
-        <v>89.85114279919175</v>
+        <v>89.51143427139154</v>
       </c>
       <c r="P38">
-        <v>203.5882523647264</v>
+        <v>202.8185274248577</v>
       </c>
       <c r="Q38">
-        <v>203.9192523647264</v>
+        <v>203.1495274248577</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08918516990490749</v>
+        <v>0.08972215009721204</v>
       </c>
       <c r="T38">
-        <v>0.823000641283975</v>
+        <v>0.833186957105535</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.34707807872006</v>
+        <v>8.121481373889786</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07025872556124359</v>
+        <v>0.07007635438334638</v>
       </c>
       <c r="C39">
-        <v>1602.393200056077</v>
+        <v>1596.830701958495</v>
       </c>
       <c r="D39">
-        <v>2019.964944051417</v>
+        <v>2035.139520115872</v>
       </c>
       <c r="E39">
-        <v>331.9643277917172</v>
+        <v>352.7014019537534</v>
       </c>
       <c r="F39">
-        <v>767.2717439953408</v>
+        <v>788.008818157377</v>
       </c>
       <c r="G39">
         <v>349.7</v>
@@ -4485,28 +4485,28 @@
         <v>333.379</v>
       </c>
       <c r="M39">
-        <v>41.04903830375073</v>
+        <v>42.15847177141967</v>
       </c>
       <c r="N39">
-        <v>292.3299616962493</v>
+        <v>291.2205282285803</v>
       </c>
       <c r="O39">
-        <v>89.51143427139154</v>
+        <v>89.1717257435913</v>
       </c>
       <c r="P39">
-        <v>202.8185274248577</v>
+        <v>202.048802484989</v>
       </c>
       <c r="Q39">
-        <v>203.1495274248577</v>
+        <v>202.379802484989</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08972215009721204</v>
+        <v>0.09027645223120383</v>
       </c>
       <c r="T39">
-        <v>0.833186957105535</v>
+        <v>0.8437018637600486</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.121481373889786</v>
+        <v>7.907758179840055</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07007635438334638</v>
+        <v>0.06989398320544915</v>
       </c>
       <c r="C40">
-        <v>1596.830701958495</v>
+        <v>1591.497921403867</v>
       </c>
       <c r="D40">
-        <v>2035.139520115872</v>
+        <v>2050.54381372328</v>
       </c>
       <c r="E40">
-        <v>352.7014019537534</v>
+        <v>373.4384761157897</v>
       </c>
       <c r="F40">
-        <v>788.008818157377</v>
+        <v>808.7458923194133</v>
       </c>
       <c r="G40">
         <v>349.7</v>
@@ -4567,28 +4567,28 @@
         <v>333.379</v>
       </c>
       <c r="M40">
-        <v>42.15847177141967</v>
+        <v>43.26790523908861</v>
       </c>
       <c r="N40">
-        <v>291.2205282285803</v>
+        <v>290.1110947609113</v>
       </c>
       <c r="O40">
-        <v>89.1717257435913</v>
+        <v>88.83201721579105</v>
       </c>
       <c r="P40">
-        <v>202.048802484989</v>
+        <v>201.2790775451203</v>
       </c>
       <c r="Q40">
-        <v>202.379802484989</v>
+        <v>201.6100775451203</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09027645223120383</v>
+        <v>0.09084892820565435</v>
       </c>
       <c r="T40">
-        <v>0.8437018637600486</v>
+        <v>0.8545615214524152</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.907758179840055</v>
+        <v>7.704995149587745</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06989398320544915</v>
+        <v>0.06993362802755194</v>
       </c>
       <c r="C41">
-        <v>1591.497921403867</v>
+        <v>1567.392375472222</v>
       </c>
       <c r="D41">
-        <v>2050.54381372328</v>
+        <v>2047.175341953672</v>
       </c>
       <c r="E41">
-        <v>373.4384761157897</v>
+        <v>394.1755502778259</v>
       </c>
       <c r="F41">
-        <v>808.7458923194133</v>
+        <v>829.4829664814496</v>
       </c>
       <c r="G41">
         <v>349.7</v>
@@ -4649,45 +4649,45 @@
         <v>333.379</v>
       </c>
       <c r="M41">
-        <v>43.26790523908861</v>
+        <v>45.04092507994271</v>
       </c>
       <c r="N41">
-        <v>290.1110947609113</v>
+        <v>288.3380749200572</v>
       </c>
       <c r="O41">
-        <v>88.83201721579105</v>
+        <v>88.28911854052153</v>
       </c>
       <c r="P41">
-        <v>201.2790775451203</v>
+        <v>200.0489563795357</v>
       </c>
       <c r="Q41">
-        <v>201.6100775451203</v>
+        <v>200.3799563795357</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09084892820565435</v>
+        <v>0.09144048671258657</v>
       </c>
       <c r="T41">
-        <v>0.8545615214524152</v>
+        <v>0.8657831677345271</v>
       </c>
       <c r="U41">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V41">
         <v>0.3062</v>
       </c>
       <c r="W41">
-        <v>0.0371183</v>
+        <v>0.03767334</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y41">
-        <v>7.704995149587745</v>
+        <v>7.401690782511432</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06993362802755194</v>
+        <v>0.06975680724965473</v>
       </c>
       <c r="C42">
-        <v>1567.392375472222</v>
+        <v>1561.765125114502</v>
       </c>
       <c r="D42">
-        <v>2047.175341953672</v>
+        <v>2062.285165757988</v>
       </c>
       <c r="E42">
-        <v>394.1755502778259</v>
+        <v>414.9126244398622</v>
       </c>
       <c r="F42">
-        <v>829.4829664814496</v>
+        <v>850.2200406434858</v>
       </c>
       <c r="G42">
         <v>349.7</v>
@@ -4731,28 +4731,28 @@
         <v>333.379</v>
       </c>
       <c r="M42">
-        <v>45.04092507994271</v>
+        <v>46.16694820694129</v>
       </c>
       <c r="N42">
-        <v>288.3380749200572</v>
+        <v>287.2120517930587</v>
       </c>
       <c r="O42">
-        <v>88.28911854052153</v>
+        <v>87.94433025903457</v>
       </c>
       <c r="P42">
-        <v>200.0489563795357</v>
+        <v>199.2677215340241</v>
       </c>
       <c r="Q42">
-        <v>200.3799563795357</v>
+        <v>199.5987215340241</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09144048671258657</v>
+        <v>0.09205209805026225</v>
       </c>
       <c r="T42">
-        <v>0.8657831677345271</v>
+        <v>0.8773852088058632</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.401690782511432</v>
+        <v>7.221161739035542</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06975680724965473</v>
+        <v>0.0695799864717575</v>
       </c>
       <c r="C43">
-        <v>1561.765125114502</v>
+        <v>1556.362578904714</v>
       </c>
       <c r="D43">
-        <v>2062.285165757988</v>
+        <v>2077.619693710236</v>
       </c>
       <c r="E43">
-        <v>414.9126244398622</v>
+        <v>435.6496986018985</v>
       </c>
       <c r="F43">
-        <v>850.2200406434858</v>
+        <v>870.9571148055221</v>
       </c>
       <c r="G43">
         <v>349.7</v>
@@ -4813,28 +4813,28 @@
         <v>333.379</v>
       </c>
       <c r="M43">
-        <v>46.16694820694129</v>
+        <v>47.29297133393985</v>
       </c>
       <c r="N43">
-        <v>287.2120517930587</v>
+        <v>286.0860286660601</v>
       </c>
       <c r="O43">
-        <v>87.94433025903457</v>
+        <v>87.5995419775476</v>
       </c>
       <c r="P43">
-        <v>199.2677215340241</v>
+        <v>198.4864866885125</v>
       </c>
       <c r="Q43">
-        <v>199.5987215340241</v>
+        <v>198.8174866885125</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09205209805026225</v>
+        <v>0.09268479943406469</v>
       </c>
       <c r="T43">
-        <v>0.8773852088058632</v>
+        <v>0.8893873202589696</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.221161739035542</v>
+        <v>7.049229316677553</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06957998647175753</v>
+        <v>0.06940316569386031</v>
       </c>
       <c r="C44">
-        <v>1556.362578904711</v>
+        <v>1551.189786889455</v>
       </c>
       <c r="D44">
-        <v>2077.619693710234</v>
+        <v>2093.183975857014</v>
       </c>
       <c r="E44">
-        <v>435.6496986018984</v>
+        <v>456.3867727639346</v>
       </c>
       <c r="F44">
-        <v>870.957114805522</v>
+        <v>891.6941889675583</v>
       </c>
       <c r="G44">
         <v>349.7</v>
@@ -4895,28 +4895,28 @@
         <v>333.379</v>
       </c>
       <c r="M44">
-        <v>47.29297133393985</v>
+        <v>48.41899446093841</v>
       </c>
       <c r="N44">
-        <v>286.0860286660601</v>
+        <v>284.9600055390616</v>
       </c>
       <c r="O44">
-        <v>87.5995419775476</v>
+        <v>87.25475369606066</v>
       </c>
       <c r="P44">
-        <v>198.4864866885125</v>
+        <v>197.7052518430009</v>
       </c>
       <c r="Q44">
-        <v>198.8174866885125</v>
+        <v>198.0362518430009</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09268479943406469</v>
+        <v>0.09333970086642157</v>
       </c>
       <c r="T44">
-        <v>0.8893873202589696</v>
+        <v>0.9018105584297288</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.049229316677554</v>
+        <v>6.885293751173426</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06940316569386031</v>
+        <v>0.06922634491596308</v>
       </c>
       <c r="C45">
-        <v>1551.189786889455</v>
+        <v>1546.251951585242</v>
       </c>
       <c r="D45">
-        <v>2093.183975857014</v>
+        <v>2108.983214714836</v>
       </c>
       <c r="E45">
-        <v>456.3867727639346</v>
+        <v>477.1238469259708</v>
       </c>
       <c r="F45">
-        <v>891.6941889675583</v>
+        <v>912.4312631295944</v>
       </c>
       <c r="G45">
         <v>349.7</v>
@@ -4977,28 +4977,28 @@
         <v>333.379</v>
       </c>
       <c r="M45">
-        <v>48.41899446093841</v>
+        <v>49.54501758793698</v>
       </c>
       <c r="N45">
-        <v>284.9600055390616</v>
+        <v>283.833982412063</v>
       </c>
       <c r="O45">
-        <v>87.25475369606066</v>
+        <v>86.90996541457369</v>
       </c>
       <c r="P45">
-        <v>197.7052518430009</v>
+        <v>196.9240169974893</v>
       </c>
       <c r="Q45">
-        <v>198.0362518430009</v>
+        <v>197.2550169974893</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09333970086642157</v>
+        <v>0.09401799163564836</v>
       </c>
       <c r="T45">
-        <v>0.9018105584297288</v>
+        <v>0.9146774836780152</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.885293751173426</v>
+        <v>6.728809802283122</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06922634491596308</v>
+        <v>0.06904952413806587</v>
       </c>
       <c r="C46">
-        <v>1546.251951585242</v>
+        <v>1541.554433776425</v>
       </c>
       <c r="D46">
-        <v>2108.983214714836</v>
+        <v>2125.022771068056</v>
       </c>
       <c r="E46">
-        <v>477.1238469259708</v>
+        <v>497.860921088007</v>
       </c>
       <c r="F46">
-        <v>912.4312631295944</v>
+        <v>933.1683372916307</v>
       </c>
       <c r="G46">
         <v>349.7</v>
@@ -5059,28 +5059,28 @@
         <v>333.379</v>
       </c>
       <c r="M46">
-        <v>49.54501758793698</v>
+        <v>50.67104071493554</v>
       </c>
       <c r="N46">
-        <v>283.833982412063</v>
+        <v>282.7079592850644</v>
       </c>
       <c r="O46">
-        <v>86.90996541457369</v>
+        <v>86.56517713308673</v>
       </c>
       <c r="P46">
-        <v>196.9240169974893</v>
+        <v>196.1427821519777</v>
       </c>
       <c r="Q46">
-        <v>197.2550169974893</v>
+        <v>196.4737821519777</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09401799163564836</v>
+        <v>0.09472094752375612</v>
       </c>
       <c r="T46">
-        <v>0.9146774836780152</v>
+        <v>0.9280122971171482</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.728809802283122</v>
+        <v>6.579280695565719</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06904952413806587</v>
+        <v>0.06887270336016865</v>
       </c>
       <c r="C47">
-        <v>1541.554433776425</v>
+        <v>1537.10275857974</v>
       </c>
       <c r="D47">
-        <v>2125.022771068056</v>
+        <v>2141.308170033407</v>
       </c>
       <c r="E47">
-        <v>497.860921088007</v>
+        <v>518.5979952500434</v>
       </c>
       <c r="F47">
-        <v>933.1683372916307</v>
+        <v>953.9054114536669</v>
       </c>
       <c r="G47">
         <v>349.7</v>
@@ -5141,28 +5141,28 @@
         <v>333.379</v>
       </c>
       <c r="M47">
-        <v>50.67104071493554</v>
+        <v>51.79706384193412</v>
       </c>
       <c r="N47">
-        <v>282.7079592850644</v>
+        <v>281.5819361580658</v>
       </c>
       <c r="O47">
-        <v>86.56517713308673</v>
+        <v>86.22038885159976</v>
       </c>
       <c r="P47">
-        <v>196.1427821519777</v>
+        <v>195.3615473064661</v>
       </c>
       <c r="Q47">
-        <v>196.4737821519777</v>
+        <v>195.6925473064661</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09472094752375612</v>
+        <v>0.09544993881512713</v>
       </c>
       <c r="T47">
-        <v>0.9280122971171482</v>
+        <v>0.9418409925355085</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.579280695565719</v>
+        <v>6.436252854357767</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06887270336016865</v>
+        <v>0.06869588258227144</v>
       </c>
       <c r="C48">
-        <v>1537.10275857974</v>
+        <v>1532.902621789847</v>
       </c>
       <c r="D48">
-        <v>2141.308170033407</v>
+        <v>2157.84510740555</v>
       </c>
       <c r="E48">
-        <v>518.5979952500434</v>
+        <v>539.3350694120795</v>
       </c>
       <c r="F48">
-        <v>953.9054114536669</v>
+        <v>974.6424856157032</v>
       </c>
       <c r="G48">
         <v>349.7</v>
@@ -5223,28 +5223,28 @@
         <v>333.379</v>
       </c>
       <c r="M48">
-        <v>51.79706384193412</v>
+        <v>52.92308696893269</v>
       </c>
       <c r="N48">
-        <v>281.5819361580658</v>
+        <v>280.4559130310673</v>
       </c>
       <c r="O48">
-        <v>86.22038885159976</v>
+        <v>85.87560057011281</v>
       </c>
       <c r="P48">
-        <v>195.3615473064661</v>
+        <v>194.5803124609545</v>
       </c>
       <c r="Q48">
-        <v>195.6925473064661</v>
+        <v>194.9113124609545</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09544993881512713</v>
+        <v>0.09620643921183289</v>
       </c>
       <c r="T48">
-        <v>0.9418409925355085</v>
+        <v>0.9561915255168257</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.436252854357767</v>
+        <v>6.299311304265048</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06869588258227144</v>
+        <v>0.06851906180437423</v>
       </c>
       <c r="C49">
-        <v>1532.902621789847</v>
+        <v>1528.9598965212</v>
       </c>
       <c r="D49">
-        <v>2157.84510740555</v>
+        <v>2174.63945629894</v>
       </c>
       <c r="E49">
-        <v>539.3350694120795</v>
+        <v>560.0721435741159</v>
       </c>
       <c r="F49">
-        <v>974.6424856157032</v>
+        <v>995.3795597777395</v>
       </c>
       <c r="G49">
         <v>349.7</v>
@@ -5305,28 +5305,28 @@
         <v>333.379</v>
       </c>
       <c r="M49">
-        <v>52.92308696893269</v>
+        <v>54.04911009593125</v>
       </c>
       <c r="N49">
-        <v>280.4559130310673</v>
+        <v>279.3298899040687</v>
       </c>
       <c r="O49">
-        <v>85.87560057011281</v>
+        <v>85.53081228862584</v>
       </c>
       <c r="P49">
-        <v>194.5803124609545</v>
+        <v>193.7990776154429</v>
       </c>
       <c r="Q49">
-        <v>194.9113124609545</v>
+        <v>194.1300776154428</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09620643921183289</v>
+        <v>0.09699203577764273</v>
       </c>
       <c r="T49">
-        <v>0.9561915255168257</v>
+        <v>0.9710940020743475</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.299311304265048</v>
+        <v>6.16807565209286</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06851906180437423</v>
+        <v>0.06868220302647701</v>
       </c>
       <c r="C50">
-        <v>1528.9598965212</v>
+        <v>1492.718487478338</v>
       </c>
       <c r="D50">
-        <v>2174.63945629894</v>
+        <v>2159.135121418114</v>
       </c>
       <c r="E50">
-        <v>560.0721435741157</v>
+        <v>580.809217736152</v>
       </c>
       <c r="F50">
-        <v>995.3795597777394</v>
+        <v>1016.116633939776</v>
       </c>
       <c r="G50">
         <v>349.7</v>
@@ -5387,45 +5387,45 @@
         <v>333.379</v>
       </c>
       <c r="M50">
-        <v>54.04911009593125</v>
+        <v>56.1912498568696</v>
       </c>
       <c r="N50">
-        <v>279.3298899040687</v>
+        <v>277.1877501431304</v>
       </c>
       <c r="O50">
-        <v>85.53081228862584</v>
+        <v>84.87488909382652</v>
       </c>
       <c r="P50">
-        <v>193.7990776154429</v>
+        <v>192.3128610493038</v>
       </c>
       <c r="Q50">
-        <v>194.1300776154428</v>
+        <v>192.6438610493038</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09699203577764273</v>
+        <v>0.0978084400519157</v>
       </c>
       <c r="T50">
-        <v>0.9710940020743475</v>
+        <v>0.9865808894772623</v>
       </c>
       <c r="U50">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V50">
         <v>0.3062</v>
       </c>
       <c r="W50">
-        <v>0.03767334</v>
+        <v>0.03836714</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>6.168075652092861</v>
+        <v>5.932934413261553</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06868220302647701</v>
+        <v>0.06851232024857978</v>
       </c>
       <c r="C51">
-        <v>1492.718487478338</v>
+        <v>1488.131232809311</v>
       </c>
       <c r="D51">
-        <v>2159.135121418114</v>
+        <v>2175.284940911123</v>
       </c>
       <c r="E51">
-        <v>580.809217736152</v>
+        <v>601.5462918981882</v>
       </c>
       <c r="F51">
-        <v>1016.116633939776</v>
+        <v>1036.853708101812</v>
       </c>
       <c r="G51">
         <v>349.7</v>
@@ -5469,28 +5469,28 @@
         <v>333.379</v>
       </c>
       <c r="M51">
-        <v>56.1912498568696</v>
+        <v>57.3380100580302</v>
       </c>
       <c r="N51">
-        <v>277.1877501431304</v>
+        <v>276.0409899419698</v>
       </c>
       <c r="O51">
-        <v>84.87488909382652</v>
+        <v>84.52375112023115</v>
       </c>
       <c r="P51">
-        <v>192.3128610493038</v>
+        <v>191.5172388217386</v>
       </c>
       <c r="Q51">
-        <v>192.6438610493038</v>
+        <v>191.8482388217386</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.0978084400519157</v>
+        <v>0.09865750049715957</v>
       </c>
       <c r="T51">
-        <v>0.9865808894772623</v>
+        <v>1.002687252376294</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.932934413261553</v>
+        <v>5.814275724996323</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06851232024857978</v>
+        <v>0.06834243747068257</v>
       </c>
       <c r="C52">
-        <v>1488.131232809311</v>
+        <v>1483.787392473944</v>
       </c>
       <c r="D52">
-        <v>2175.284940911123</v>
+        <v>2191.678174737792</v>
       </c>
       <c r="E52">
-        <v>601.5462918981882</v>
+        <v>622.2833660602244</v>
       </c>
       <c r="F52">
-        <v>1036.853708101812</v>
+        <v>1057.590782263848</v>
       </c>
       <c r="G52">
         <v>349.7</v>
@@ -5551,28 +5551,28 @@
         <v>333.379</v>
       </c>
       <c r="M52">
-        <v>57.3380100580302</v>
+        <v>58.4847702591908</v>
       </c>
       <c r="N52">
-        <v>276.0409899419698</v>
+        <v>274.8942297408092</v>
       </c>
       <c r="O52">
-        <v>84.52375112023115</v>
+        <v>84.17261314663578</v>
       </c>
       <c r="P52">
-        <v>191.5172388217386</v>
+        <v>190.7216165941734</v>
       </c>
       <c r="Q52">
-        <v>191.8482388217386</v>
+        <v>191.0526165941734</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09865750049715957</v>
+        <v>0.09954121647078076</v>
       </c>
       <c r="T52">
-        <v>1.002687252376294</v>
+        <v>1.019451017842632</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.814275724996323</v>
+        <v>5.700270318623846</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06834243747068257</v>
+        <v>0.06817255469278537</v>
       </c>
       <c r="C53">
-        <v>1483.787392473944</v>
+        <v>1479.692511467488</v>
       </c>
       <c r="D53">
-        <v>2191.678174737792</v>
+        <v>2208.320367893372</v>
       </c>
       <c r="E53">
-        <v>622.2833660602244</v>
+        <v>643.0204402222607</v>
       </c>
       <c r="F53">
-        <v>1057.590782263848</v>
+        <v>1078.327856425884</v>
       </c>
       <c r="G53">
         <v>349.7</v>
@@ -5633,28 +5633,28 @@
         <v>333.379</v>
       </c>
       <c r="M53">
-        <v>58.4847702591908</v>
+        <v>59.63153046035141</v>
       </c>
       <c r="N53">
-        <v>274.8942297408092</v>
+        <v>273.7474695396485</v>
       </c>
       <c r="O53">
-        <v>84.17261314663578</v>
+        <v>83.82147517304038</v>
       </c>
       <c r="P53">
-        <v>190.7216165941734</v>
+        <v>189.9259943666082</v>
       </c>
       <c r="Q53">
-        <v>191.0526165941734</v>
+        <v>190.2569943666082</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09954121647078076</v>
+        <v>0.1004617539433028</v>
       </c>
       <c r="T53">
-        <v>1.019451017842632</v>
+        <v>1.036913273536735</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.700270318623846</v>
+        <v>5.590649735573386</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06817255469278537</v>
+        <v>0.06800267191488814</v>
       </c>
       <c r="C54">
-        <v>1479.692511467488</v>
+        <v>1475.852304494359</v>
       </c>
       <c r="D54">
-        <v>2208.320367893372</v>
+        <v>2225.21723508228</v>
       </c>
       <c r="E54">
-        <v>643.0204402222607</v>
+        <v>663.7575143842969</v>
       </c>
       <c r="F54">
-        <v>1078.327856425884</v>
+        <v>1099.064930587921</v>
       </c>
       <c r="G54">
         <v>349.7</v>
@@ -5715,28 +5715,28 @@
         <v>333.379</v>
       </c>
       <c r="M54">
-        <v>59.63153046035141</v>
+        <v>60.77829066151201</v>
       </c>
       <c r="N54">
-        <v>273.7474695396485</v>
+        <v>272.6007093384879</v>
       </c>
       <c r="O54">
-        <v>83.82147517304038</v>
+        <v>83.47033719944501</v>
       </c>
       <c r="P54">
-        <v>189.9259943666082</v>
+        <v>189.1303721390429</v>
       </c>
       <c r="Q54">
-        <v>190.2569943666082</v>
+        <v>189.4613721390429</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1004617539433028</v>
+        <v>0.1014214632231663</v>
       </c>
       <c r="T54">
-        <v>1.036913273536735</v>
+        <v>1.055118603941225</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.590649735573386</v>
+        <v>5.485165778298417</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06800267191488814</v>
+        <v>0.06783278913699094</v>
       </c>
       <c r="C55">
-        <v>1475.852304494359</v>
+        <v>1472.272662510795</v>
       </c>
       <c r="D55">
-        <v>2225.21723508228</v>
+        <v>2242.374667260753</v>
       </c>
       <c r="E55">
-        <v>663.7575143842969</v>
+        <v>684.4945885463333</v>
       </c>
       <c r="F55">
-        <v>1099.064930587921</v>
+        <v>1119.802004749957</v>
       </c>
       <c r="G55">
         <v>349.7</v>
@@ -5797,28 +5797,28 @@
         <v>333.379</v>
       </c>
       <c r="M55">
-        <v>60.77829066151201</v>
+        <v>61.92505086267262</v>
       </c>
       <c r="N55">
-        <v>272.6007093384879</v>
+        <v>271.4539491373274</v>
       </c>
       <c r="O55">
-        <v>83.47033719944501</v>
+        <v>83.11919922584964</v>
       </c>
       <c r="P55">
-        <v>189.1303721390429</v>
+        <v>188.3347499114777</v>
       </c>
       <c r="Q55">
-        <v>189.4613721390429</v>
+        <v>188.6657499114777</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1014214632231663</v>
+        <v>0.1024228989934585</v>
       </c>
       <c r="T55">
-        <v>1.055118603941225</v>
+        <v>1.074115470450259</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.485165778298417</v>
+        <v>5.383588634255854</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06783278913699094</v>
+        <v>0.06766290635909371</v>
       </c>
       <c r="C56">
-        <v>1472.272662510795</v>
+        <v>1468.959659572583</v>
       </c>
       <c r="D56">
-        <v>2242.374667260753</v>
+        <v>2259.798738484576</v>
       </c>
       <c r="E56">
-        <v>684.4945885463333</v>
+        <v>705.2316627083694</v>
       </c>
       <c r="F56">
-        <v>1119.802004749957</v>
+        <v>1140.539078911993</v>
       </c>
       <c r="G56">
         <v>349.7</v>
@@ -5879,28 +5879,28 @@
         <v>333.379</v>
       </c>
       <c r="M56">
-        <v>61.92505086267262</v>
+        <v>63.07181106383322</v>
       </c>
       <c r="N56">
-        <v>271.4539491373274</v>
+        <v>270.3071889361668</v>
       </c>
       <c r="O56">
-        <v>83.11919922584964</v>
+        <v>82.76806125225427</v>
       </c>
       <c r="P56">
-        <v>188.3347499114777</v>
+        <v>187.5391276839125</v>
       </c>
       <c r="Q56">
-        <v>188.6657499114777</v>
+        <v>187.8701276839125</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1024228989934585</v>
+        <v>0.1034688430202083</v>
       </c>
       <c r="T56">
-        <v>1.074115470450259</v>
+        <v>1.093956642137471</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.383588634255854</v>
+        <v>5.285705204542111</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06766290635909371</v>
+        <v>0.06749302358119649</v>
       </c>
       <c r="C57">
-        <v>1468.959659572583</v>
+        <v>1465.919560004496</v>
       </c>
       <c r="D57">
-        <v>2259.798738484576</v>
+        <v>2277.495713078526</v>
       </c>
       <c r="E57">
-        <v>705.2316627083694</v>
+        <v>725.9687368704058</v>
       </c>
       <c r="F57">
-        <v>1140.539078911993</v>
+        <v>1161.276153074029</v>
       </c>
       <c r="G57">
         <v>349.7</v>
@@ -5961,28 +5961,28 @@
         <v>333.379</v>
       </c>
       <c r="M57">
-        <v>63.07181106383322</v>
+        <v>64.21857126499383</v>
       </c>
       <c r="N57">
-        <v>270.3071889361668</v>
+        <v>269.1604287350061</v>
       </c>
       <c r="O57">
-        <v>82.76806125225427</v>
+        <v>82.41692327865889</v>
       </c>
       <c r="P57">
-        <v>187.5391276839125</v>
+        <v>186.7435054563472</v>
       </c>
       <c r="Q57">
-        <v>187.8701276839125</v>
+        <v>187.0745054563472</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1034688430202083</v>
+        <v>0.1045623299572648</v>
       </c>
       <c r="T57">
-        <v>1.093956642137471</v>
+        <v>1.114699685265012</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.285705204542111</v>
+        <v>5.191317611603859</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06749302358119649</v>
+        <v>0.06732314080329929</v>
       </c>
       <c r="C58">
-        <v>1465.919560004496</v>
+        <v>1463.158825909307</v>
       </c>
       <c r="D58">
-        <v>2277.495713078526</v>
+        <v>2295.472053145373</v>
       </c>
       <c r="E58">
-        <v>725.9687368704058</v>
+        <v>746.7058110324419</v>
       </c>
       <c r="F58">
-        <v>1161.276153074029</v>
+        <v>1182.013227236066</v>
       </c>
       <c r="G58">
         <v>349.7</v>
@@ -6043,28 +6043,28 @@
         <v>333.379</v>
       </c>
       <c r="M58">
-        <v>64.21857126499383</v>
+        <v>65.36533146615443</v>
       </c>
       <c r="N58">
-        <v>269.1604287350061</v>
+        <v>268.0136685338455</v>
       </c>
       <c r="O58">
-        <v>82.41692327865889</v>
+        <v>82.06578530506351</v>
       </c>
       <c r="P58">
-        <v>186.7435054563472</v>
+        <v>185.947883228782</v>
       </c>
       <c r="Q58">
-        <v>187.0745054563472</v>
+        <v>186.278883228782</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1045623299572648</v>
+        <v>0.1057066767518588</v>
       </c>
       <c r="T58">
-        <v>1.114699685265012</v>
+        <v>1.136407521096159</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.191317611603859</v>
+        <v>5.100241864031862</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06732314080329929</v>
+        <v>0.06715325802540208</v>
       </c>
       <c r="C59">
-        <v>1463.158825909307</v>
+        <v>1460.684125035219</v>
       </c>
       <c r="D59">
-        <v>2295.472053145373</v>
+        <v>2313.734426433321</v>
       </c>
       <c r="E59">
-        <v>746.7058110324419</v>
+        <v>767.4428851944783</v>
       </c>
       <c r="F59">
-        <v>1182.013227236066</v>
+        <v>1202.750301398102</v>
       </c>
       <c r="G59">
         <v>349.7</v>
@@ -6125,28 +6125,28 @@
         <v>333.379</v>
       </c>
       <c r="M59">
-        <v>65.36533146615443</v>
+        <v>66.51209166731505</v>
       </c>
       <c r="N59">
-        <v>268.0136685338455</v>
+        <v>266.8669083326849</v>
       </c>
       <c r="O59">
-        <v>82.06578530506351</v>
+        <v>81.71464733146814</v>
       </c>
       <c r="P59">
-        <v>185.947883228782</v>
+        <v>185.1522610012168</v>
       </c>
       <c r="Q59">
-        <v>186.278883228782</v>
+        <v>185.4832610012168</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1057066767518588</v>
+        <v>0.1069055162509573</v>
       </c>
       <c r="T59">
-        <v>1.136407521096159</v>
+        <v>1.159149063395456</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.100241864031862</v>
+        <v>5.012306659479587</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.06715325802540206</v>
+        <v>0.06698337524750486</v>
       </c>
       <c r="C60">
-        <v>1460.68412503522</v>
+        <v>1458.502339021855</v>
       </c>
       <c r="D60">
-        <v>2313.734426433322</v>
+        <v>2332.289714581993</v>
       </c>
       <c r="E60">
-        <v>767.4428851944781</v>
+        <v>788.1799593565142</v>
       </c>
       <c r="F60">
-        <v>1202.750301398102</v>
+        <v>1223.487375560138</v>
       </c>
       <c r="G60">
         <v>349.7</v>
@@ -6207,28 +6207,28 @@
         <v>333.379</v>
       </c>
       <c r="M60">
-        <v>66.51209166731503</v>
+        <v>67.65885186847564</v>
       </c>
       <c r="N60">
-        <v>266.8669083326849</v>
+        <v>265.7201481315243</v>
       </c>
       <c r="O60">
-        <v>81.71464733146814</v>
+        <v>81.36350935787274</v>
       </c>
       <c r="P60">
-        <v>185.1522610012168</v>
+        <v>184.3566387736516</v>
       </c>
       <c r="Q60">
-        <v>185.4832610012168</v>
+        <v>184.6876387736515</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1069055162509573</v>
+        <v>0.1081628357256216</v>
       </c>
       <c r="T60">
-        <v>1.159149063395455</v>
+        <v>1.182999949221547</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.012306659479588</v>
+        <v>4.927352309318916</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.06698337524750486</v>
+        <v>0.06681349246960763</v>
       </c>
       <c r="C61">
-        <v>1458.502339021855</v>
+        <v>1456.620572046256</v>
       </c>
       <c r="D61">
-        <v>2332.289714581993</v>
+        <v>2351.14502176843</v>
       </c>
       <c r="E61">
-        <v>788.1799593565142</v>
+        <v>808.9170335185506</v>
       </c>
       <c r="F61">
-        <v>1223.487375560138</v>
+        <v>1244.224449722174</v>
       </c>
       <c r="G61">
         <v>349.7</v>
@@ -6289,28 +6289,28 @@
         <v>333.379</v>
       </c>
       <c r="M61">
-        <v>67.65885186847564</v>
+        <v>68.80561206963624</v>
       </c>
       <c r="N61">
-        <v>265.7201481315243</v>
+        <v>264.5733879303637</v>
       </c>
       <c r="O61">
-        <v>81.36350935787274</v>
+        <v>81.01237138427737</v>
       </c>
       <c r="P61">
-        <v>184.3566387736516</v>
+        <v>183.5610165460863</v>
       </c>
       <c r="Q61">
-        <v>184.6876387736515</v>
+        <v>183.8920165460863</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1081628357256216</v>
+        <v>0.1094830211740191</v>
       </c>
       <c r="T61">
-        <v>1.182999949221547</v>
+        <v>1.208043379338943</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.927352309318916</v>
+        <v>4.845229770830269</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.06681349246960763</v>
+        <v>0.06664360969171042</v>
       </c>
       <c r="C62">
-        <v>1456.620572046256</v>
+        <v>1455.046159891659</v>
       </c>
       <c r="D62">
-        <v>2351.14502176843</v>
+        <v>2370.307683775869</v>
       </c>
       <c r="E62">
-        <v>808.9170335185506</v>
+        <v>829.6541076805868</v>
       </c>
       <c r="F62">
-        <v>1244.224449722174</v>
+        <v>1264.96152388421</v>
       </c>
       <c r="G62">
         <v>349.7</v>
@@ -6371,28 +6371,28 @@
         <v>333.379</v>
       </c>
       <c r="M62">
-        <v>68.80561206963624</v>
+        <v>69.95237227079684</v>
       </c>
       <c r="N62">
-        <v>264.5733879303637</v>
+        <v>263.4266277292031</v>
       </c>
       <c r="O62">
-        <v>81.01237138427737</v>
+        <v>80.661233410682</v>
       </c>
       <c r="P62">
-        <v>183.5610165460863</v>
+        <v>182.7653943185211</v>
       </c>
       <c r="Q62">
-        <v>183.8920165460863</v>
+        <v>183.0963943185211</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1094830211740191</v>
+        <v>0.1108709084402831</v>
       </c>
       <c r="T62">
-        <v>1.208043379338943</v>
+        <v>1.234371087923898</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.845229770830269</v>
+        <v>4.765799774587149</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.06664360969171042</v>
+        <v>0.06647372691381322</v>
       </c>
       <c r="C63">
-        <v>1455.046159891659</v>
+        <v>1453.786679463429</v>
       </c>
       <c r="D63">
-        <v>2370.307683775869</v>
+        <v>2389.785277509676</v>
       </c>
       <c r="E63">
-        <v>829.6541076805868</v>
+        <v>850.3911818426232</v>
       </c>
       <c r="F63">
-        <v>1264.96152388421</v>
+        <v>1285.698598046247</v>
       </c>
       <c r="G63">
         <v>349.7</v>
@@ -6453,28 +6453,28 @@
         <v>333.379</v>
       </c>
       <c r="M63">
-        <v>69.95237227079684</v>
+        <v>71.09913247195745</v>
       </c>
       <c r="N63">
-        <v>263.4266277292031</v>
+        <v>262.2798675280425</v>
       </c>
       <c r="O63">
-        <v>80.661233410682</v>
+        <v>80.31009543708663</v>
       </c>
       <c r="P63">
-        <v>182.7653943185211</v>
+        <v>181.9697720909559</v>
       </c>
       <c r="Q63">
-        <v>183.0963943185211</v>
+        <v>182.3007720909559</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1108709084402831</v>
+        <v>0.1123318424047716</v>
       </c>
       <c r="T63">
-        <v>1.234371087923898</v>
+        <v>1.262084465381746</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.765799774587149</v>
+        <v>4.688932036287357</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.06647372691381322</v>
+        <v>0.066303844135916</v>
       </c>
       <c r="C64">
-        <v>1453.786679463429</v>
+        <v>1452.84995877804</v>
       </c>
       <c r="D64">
-        <v>2389.785277509676</v>
+        <v>2409.585630986323</v>
       </c>
       <c r="E64">
-        <v>850.3911818426232</v>
+        <v>871.1282560046593</v>
       </c>
       <c r="F64">
-        <v>1285.698598046247</v>
+        <v>1306.435672208283</v>
       </c>
       <c r="G64">
         <v>349.7</v>
@@ -6535,28 +6535,28 @@
         <v>333.379</v>
       </c>
       <c r="M64">
-        <v>71.09913247195745</v>
+        <v>72.24589267311805</v>
       </c>
       <c r="N64">
-        <v>262.2798675280425</v>
+        <v>261.1331073268819</v>
       </c>
       <c r="O64">
-        <v>80.31009543708663</v>
+        <v>79.95895746349126</v>
       </c>
       <c r="P64">
-        <v>181.9697720909559</v>
+        <v>181.1741498633907</v>
       </c>
       <c r="Q64">
-        <v>182.3007720909559</v>
+        <v>181.5051498633907</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1123318424047716</v>
+        <v>0.1138717457727459</v>
       </c>
       <c r="T64">
-        <v>1.262084465381746</v>
+        <v>1.29129586324272</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.688932036287357</v>
+        <v>4.614504543647875</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.066303844135916</v>
+        <v>0.06613396135801879</v>
       </c>
       <c r="C65">
-        <v>1452.84995877804</v>
+        <v>1452.244087452766</v>
       </c>
       <c r="D65">
-        <v>2409.585630986323</v>
+        <v>2429.716833823085</v>
       </c>
       <c r="E65">
-        <v>871.1282560046593</v>
+        <v>891.8653301666955</v>
       </c>
       <c r="F65">
-        <v>1306.435672208283</v>
+        <v>1327.172746370319</v>
       </c>
       <c r="G65">
         <v>349.7</v>
@@ -6617,28 +6617,28 @@
         <v>333.379</v>
       </c>
       <c r="M65">
-        <v>72.24589267311805</v>
+        <v>73.39265287427865</v>
       </c>
       <c r="N65">
-        <v>261.1331073268819</v>
+        <v>259.9863471257213</v>
       </c>
       <c r="O65">
-        <v>79.95895746349126</v>
+        <v>79.60781948989587</v>
       </c>
       <c r="P65">
-        <v>181.1741498633907</v>
+        <v>180.3785276358254</v>
       </c>
       <c r="Q65">
-        <v>181.5051498633907</v>
+        <v>180.7095276358254</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1138717457727459</v>
+        <v>0.11549719932783</v>
       </c>
       <c r="T65">
-        <v>1.29129586324272</v>
+        <v>1.322130116540415</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.614504543647875</v>
+        <v>4.542402910153377</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.06613396135801879</v>
+        <v>0.06709150358012157</v>
       </c>
       <c r="C66">
-        <v>1452.244087452766</v>
+        <v>1322.235422987843</v>
       </c>
       <c r="D66">
-        <v>2429.716833823085</v>
+        <v>2320.445243520198</v>
       </c>
       <c r="E66">
-        <v>891.8653301666955</v>
+        <v>912.6024043287318</v>
       </c>
       <c r="F66">
-        <v>1327.172746370319</v>
+        <v>1347.909820532356</v>
       </c>
       <c r="G66">
         <v>349.7</v>
@@ -6699,45 +6699,45 @@
         <v>333.379</v>
       </c>
       <c r="M66">
-        <v>73.39265287427865</v>
+        <v>77.90918762677015</v>
       </c>
       <c r="N66">
-        <v>259.9863471257213</v>
+        <v>255.4698123732298</v>
       </c>
       <c r="O66">
-        <v>79.60781948989587</v>
+        <v>78.22485654868298</v>
       </c>
       <c r="P66">
-        <v>180.3785276358254</v>
+        <v>177.2449558245468</v>
       </c>
       <c r="Q66">
-        <v>180.7095276358254</v>
+        <v>177.5759558245468</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.11549719932783</v>
+        <v>0.1172155359432045</v>
       </c>
       <c r="T66">
-        <v>1.322130116540415</v>
+        <v>1.354726327169408</v>
       </c>
       <c r="U66">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V66">
         <v>0.3062</v>
       </c>
       <c r="W66">
-        <v>0.03836714</v>
+        <v>0.04010164</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>4.542402910153377</v>
+        <v>4.279071700722606</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.06709150358012157</v>
+        <v>0.06693896580222436</v>
       </c>
       <c r="C67">
-        <v>1322.235422987843</v>
+        <v>1318.242572005423</v>
       </c>
       <c r="D67">
-        <v>2320.445243520198</v>
+        <v>2337.189466699815</v>
       </c>
       <c r="E67">
-        <v>912.6024043287318</v>
+        <v>933.339478490768</v>
       </c>
       <c r="F67">
-        <v>1347.909820532356</v>
+        <v>1368.646894694392</v>
       </c>
       <c r="G67">
         <v>349.7</v>
@@ -6781,28 +6781,28 @@
         <v>333.379</v>
       </c>
       <c r="M67">
-        <v>77.90918762677015</v>
+        <v>79.10779051333584</v>
       </c>
       <c r="N67">
-        <v>255.4698123732298</v>
+        <v>254.2712094866641</v>
       </c>
       <c r="O67">
-        <v>78.22485654868298</v>
+        <v>77.85784434481657</v>
       </c>
       <c r="P67">
-        <v>177.2449558245468</v>
+        <v>176.4133651418476</v>
       </c>
       <c r="Q67">
-        <v>177.5759558245468</v>
+        <v>176.7443651418476</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1172155359432045</v>
+        <v>0.1190349511830128</v>
       </c>
       <c r="T67">
-        <v>1.354726327169408</v>
+        <v>1.389239961953046</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.279071700722606</v>
+        <v>4.214237281014688</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.06693896580222436</v>
+        <v>0.06678642802432713</v>
       </c>
       <c r="C68">
-        <v>1318.242572005423</v>
+        <v>1314.49312848553</v>
       </c>
       <c r="D68">
-        <v>2337.189466699815</v>
+        <v>2354.177097341958</v>
       </c>
       <c r="E68">
-        <v>933.339478490768</v>
+        <v>954.0765526528044</v>
       </c>
       <c r="F68">
-        <v>1368.646894694392</v>
+        <v>1389.383968856428</v>
       </c>
       <c r="G68">
         <v>349.7</v>
@@ -6863,28 +6863,28 @@
         <v>333.379</v>
       </c>
       <c r="M68">
-        <v>79.10779051333584</v>
+        <v>80.30639339990155</v>
       </c>
       <c r="N68">
-        <v>254.2712094866641</v>
+        <v>253.0726066000984</v>
       </c>
       <c r="O68">
-        <v>77.85784434481657</v>
+        <v>77.49083214095015</v>
       </c>
       <c r="P68">
-        <v>176.4133651418476</v>
+        <v>175.5817744591483</v>
       </c>
       <c r="Q68">
-        <v>176.7443651418476</v>
+        <v>175.9127744591483</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1190349511830128</v>
+        <v>0.1209646340131125</v>
       </c>
       <c r="T68">
-        <v>1.389239961953046</v>
+        <v>1.425845332178117</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.214237281014688</v>
+        <v>4.151338217118946</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.06678642802432713</v>
+        <v>0.06663389024642993</v>
       </c>
       <c r="C69">
-        <v>1314.49312848553</v>
+        <v>1310.992438837258</v>
       </c>
       <c r="D69">
-        <v>2354.177097341958</v>
+        <v>2371.413481855722</v>
       </c>
       <c r="E69">
-        <v>954.0765526528044</v>
+        <v>974.8136268148405</v>
       </c>
       <c r="F69">
-        <v>1389.383968856428</v>
+        <v>1410.121043018464</v>
       </c>
       <c r="G69">
         <v>349.7</v>
@@ -6945,28 +6945,28 @@
         <v>333.379</v>
       </c>
       <c r="M69">
-        <v>80.30639339990155</v>
+        <v>81.50499628646723</v>
       </c>
       <c r="N69">
-        <v>253.0726066000984</v>
+        <v>251.8740037135327</v>
       </c>
       <c r="O69">
-        <v>77.49083214095015</v>
+        <v>77.12381993708372</v>
       </c>
       <c r="P69">
-        <v>175.5817744591483</v>
+        <v>174.750183776449</v>
       </c>
       <c r="Q69">
-        <v>175.9127744591483</v>
+        <v>175.081183776449</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1209646340131125</v>
+        <v>0.1230149220200935</v>
       </c>
       <c r="T69">
-        <v>1.425845332178117</v>
+        <v>1.464738538042256</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.151338217118946</v>
+        <v>4.090289125690726</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.06663389024642993</v>
+        <v>0.06648135246853271</v>
       </c>
       <c r="C70">
-        <v>1310.992438837258</v>
+        <v>1307.746007202019</v>
       </c>
       <c r="D70">
-        <v>2371.413481855722</v>
+        <v>2388.90412438252</v>
       </c>
       <c r="E70">
-        <v>974.8136268148405</v>
+        <v>995.5507009768769</v>
       </c>
       <c r="F70">
-        <v>1410.121043018464</v>
+        <v>1430.858117180501</v>
       </c>
       <c r="G70">
         <v>349.7</v>
@@ -7027,28 +7027,28 @@
         <v>333.379</v>
       </c>
       <c r="M70">
-        <v>81.50499628646723</v>
+        <v>82.70359917303294</v>
       </c>
       <c r="N70">
-        <v>251.8740037135327</v>
+        <v>250.675400826967</v>
       </c>
       <c r="O70">
-        <v>77.12381993708372</v>
+        <v>76.7568077332173</v>
       </c>
       <c r="P70">
-        <v>174.750183776449</v>
+        <v>173.9185930937497</v>
       </c>
       <c r="Q70">
-        <v>175.081183776449</v>
+        <v>174.2495930937497</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1230149220200935</v>
+        <v>0.1251974866726862</v>
       </c>
       <c r="T70">
-        <v>1.464738538042256</v>
+        <v>1.506140982994403</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.090289125690726</v>
+        <v>4.031009573144483</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.06648135246853271</v>
+        <v>0.0680286246906355</v>
       </c>
       <c r="C71">
-        <v>1307.746007202019</v>
+        <v>1120.724016884956</v>
       </c>
       <c r="D71">
-        <v>2388.90412438252</v>
+        <v>2222.619208227493</v>
       </c>
       <c r="E71">
-        <v>995.5507009768769</v>
+        <v>1016.287775138913</v>
       </c>
       <c r="F71">
-        <v>1430.858117180501</v>
+        <v>1451.595191342537</v>
       </c>
       <c r="G71">
         <v>349.7</v>
@@ -7109,45 +7109,45 @@
         <v>333.379</v>
       </c>
       <c r="M71">
-        <v>82.70359917303294</v>
+        <v>88.98278522929751</v>
       </c>
       <c r="N71">
-        <v>250.675400826967</v>
+        <v>244.3962147707024</v>
       </c>
       <c r="O71">
-        <v>76.7568077332173</v>
+        <v>74.8341209627891</v>
       </c>
       <c r="P71">
-        <v>173.9185930937497</v>
+        <v>169.5620938079134</v>
       </c>
       <c r="Q71">
-        <v>174.2495930937497</v>
+        <v>169.8930938079133</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1251974866726862</v>
+        <v>0.1275255556354517</v>
       </c>
       <c r="T71">
-        <v>1.506140982994403</v>
+        <v>1.55030359094336</v>
       </c>
       <c r="U71">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V71">
         <v>0.3062</v>
       </c>
       <c r="W71">
-        <v>0.04010164</v>
+        <v>0.04252994</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>4.031009573144483</v>
+        <v>3.746556136009049</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0680286246906355</v>
+        <v>0.06790036991273828</v>
       </c>
       <c r="C72">
-        <v>1120.724016884956</v>
+        <v>1112.885438722166</v>
       </c>
       <c r="D72">
-        <v>2222.619208227493</v>
+        <v>2235.51770422674</v>
       </c>
       <c r="E72">
-        <v>1016.287775138913</v>
+        <v>1037.024849300949</v>
       </c>
       <c r="F72">
-        <v>1451.595191342537</v>
+        <v>1472.332265504573</v>
       </c>
       <c r="G72">
         <v>349.7</v>
@@ -7191,28 +7191,28 @@
         <v>333.379</v>
       </c>
       <c r="M72">
-        <v>88.98278522929751</v>
+        <v>90.25396787543033</v>
       </c>
       <c r="N72">
-        <v>244.3962147707024</v>
+        <v>243.1250321245696</v>
       </c>
       <c r="O72">
-        <v>74.8341209627891</v>
+        <v>74.44488483654322</v>
       </c>
       <c r="P72">
-        <v>169.5620938079134</v>
+        <v>168.6801472880264</v>
       </c>
       <c r="Q72">
-        <v>169.8930938079133</v>
+        <v>169.0111472880264</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1275255556354517</v>
+        <v>0.1300141810784079</v>
       </c>
       <c r="T72">
-        <v>1.55030359094336</v>
+        <v>1.597511895992245</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.746556136009049</v>
+        <v>3.693787739727231</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.06790036991273828</v>
+        <v>0.06777211513484106</v>
       </c>
       <c r="C73">
-        <v>1112.885438722167</v>
+        <v>1105.197441760087</v>
       </c>
       <c r="D73">
-        <v>2235.51770422674</v>
+        <v>2248.566781426697</v>
       </c>
       <c r="E73">
-        <v>1037.024849300949</v>
+        <v>1057.761923462985</v>
       </c>
       <c r="F73">
-        <v>1472.332265504573</v>
+        <v>1493.069339666609</v>
       </c>
       <c r="G73">
         <v>349.7</v>
@@ -7273,28 +7273,28 @@
         <v>333.379</v>
       </c>
       <c r="M73">
-        <v>90.25396787543032</v>
+        <v>91.52515052156313</v>
       </c>
       <c r="N73">
-        <v>243.1250321245697</v>
+        <v>241.8538494784368</v>
       </c>
       <c r="O73">
-        <v>74.44488483654324</v>
+        <v>74.05564871029736</v>
       </c>
       <c r="P73">
-        <v>168.6801472880264</v>
+        <v>167.7982007681395</v>
       </c>
       <c r="Q73">
-        <v>169.0111472880264</v>
+        <v>168.1292007681394</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1300141810784078</v>
+        <v>0.1326805654815752</v>
       </c>
       <c r="T73">
-        <v>1.597511895992245</v>
+        <v>1.648092222830336</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.693787739727232</v>
+        <v>3.642485132231021</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.06777211513484106</v>
+        <v>0.06764386035694385</v>
       </c>
       <c r="C74">
-        <v>1105.197441760087</v>
+        <v>1097.662678381331</v>
       </c>
       <c r="D74">
-        <v>2248.566781426697</v>
+        <v>2261.769092209976</v>
       </c>
       <c r="E74">
-        <v>1057.761923462985</v>
+        <v>1078.498997625022</v>
       </c>
       <c r="F74">
-        <v>1493.069339666609</v>
+        <v>1513.806413828645</v>
       </c>
       <c r="G74">
         <v>349.7</v>
@@ -7355,28 +7355,28 @@
         <v>333.379</v>
       </c>
       <c r="M74">
-        <v>91.52515052156313</v>
+        <v>92.79633316769596</v>
       </c>
       <c r="N74">
-        <v>241.8538494784368</v>
+        <v>240.582666832304</v>
       </c>
       <c r="O74">
-        <v>74.05564871029736</v>
+        <v>73.66641258405149</v>
       </c>
       <c r="P74">
-        <v>167.7982007681395</v>
+        <v>166.9162542482525</v>
       </c>
       <c r="Q74">
-        <v>168.1292007681394</v>
+        <v>167.2472542482525</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1326805654815752</v>
+        <v>0.1355444598405328</v>
       </c>
       <c r="T74">
-        <v>1.648092222830336</v>
+        <v>1.702419240545322</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.642485132231021</v>
+        <v>3.592588075625116</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.06764386035694385</v>
+        <v>0.06751560557904662</v>
       </c>
       <c r="C75">
-        <v>1097.662678381331</v>
+        <v>1090.283863629574</v>
       </c>
       <c r="D75">
-        <v>2261.769092209976</v>
+        <v>2275.127351620255</v>
       </c>
       <c r="E75">
-        <v>1078.498997625022</v>
+        <v>1099.236071787058</v>
       </c>
       <c r="F75">
-        <v>1513.806413828645</v>
+        <v>1534.543487990682</v>
       </c>
       <c r="G75">
         <v>349.7</v>
@@ -7437,28 +7437,28 @@
         <v>333.379</v>
       </c>
       <c r="M75">
-        <v>92.79633316769596</v>
+        <v>94.06751581382878</v>
       </c>
       <c r="N75">
-        <v>240.582666832304</v>
+        <v>239.3114841861712</v>
       </c>
       <c r="O75">
-        <v>73.66641258405149</v>
+        <v>73.27717645780562</v>
       </c>
       <c r="P75">
-        <v>166.9162542482525</v>
+        <v>166.0343077283655</v>
       </c>
       <c r="Q75">
-        <v>167.2472542482525</v>
+        <v>166.3653077283655</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1355444598405328</v>
+        <v>0.138628653765564</v>
       </c>
       <c r="T75">
-        <v>1.702419240545322</v>
+        <v>1.760925259623001</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.592588075625116</v>
+        <v>3.544039588116669</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.06751560557904662</v>
+        <v>0.06884433080114942</v>
       </c>
       <c r="C76">
-        <v>1090.283863629574</v>
+        <v>938.3640217109232</v>
       </c>
       <c r="D76">
-        <v>2275.127351620255</v>
+        <v>2143.944583863641</v>
       </c>
       <c r="E76">
-        <v>1099.236071787058</v>
+        <v>1119.973145949094</v>
       </c>
       <c r="F76">
-        <v>1534.543487990682</v>
+        <v>1555.280562152718</v>
       </c>
       <c r="G76">
         <v>349.7</v>
@@ -7519,45 +7519,45 @@
         <v>333.379</v>
       </c>
       <c r="M76">
-        <v>94.06751581382878</v>
+        <v>99.69348403398921</v>
       </c>
       <c r="N76">
-        <v>239.3114841861712</v>
+        <v>233.6855159660108</v>
       </c>
       <c r="O76">
-        <v>73.27717645780562</v>
+        <v>71.5545049887925</v>
       </c>
       <c r="P76">
-        <v>166.0343077283655</v>
+        <v>162.1310109772183</v>
       </c>
       <c r="Q76">
-        <v>166.3653077283655</v>
+        <v>162.4620109772183</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.138628653765564</v>
+        <v>0.1419595832045977</v>
       </c>
       <c r="T76">
-        <v>1.760925259623001</v>
+        <v>1.824111760226893</v>
       </c>
       <c r="U76">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V76">
         <v>0.3062</v>
       </c>
       <c r="W76">
-        <v>0.04252994</v>
+        <v>0.04447258</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y76">
-        <v>3.544039588116669</v>
+        <v>3.344040016560548</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.06884433080114942</v>
+        <v>0.0687355024232522</v>
       </c>
       <c r="C77">
-        <v>938.3640217109232</v>
+        <v>927.7999102796646</v>
       </c>
       <c r="D77">
-        <v>2143.944583863641</v>
+        <v>2154.117546594419</v>
       </c>
       <c r="E77">
-        <v>1119.973145949094</v>
+        <v>1140.71022011113</v>
       </c>
       <c r="F77">
-        <v>1555.280562152718</v>
+        <v>1576.017636314754</v>
       </c>
       <c r="G77">
         <v>349.7</v>
@@ -7601,28 +7601,28 @@
         <v>333.379</v>
       </c>
       <c r="M77">
-        <v>99.69348403398921</v>
+        <v>101.0227304877757</v>
       </c>
       <c r="N77">
-        <v>233.6855159660108</v>
+        <v>232.3562695122242</v>
       </c>
       <c r="O77">
-        <v>71.5545049887925</v>
+        <v>71.14748972464307</v>
       </c>
       <c r="P77">
-        <v>162.1310109772183</v>
+        <v>161.2087797875812</v>
       </c>
       <c r="Q77">
-        <v>162.4620109772183</v>
+        <v>161.5397797875812</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1419595832045977</v>
+        <v>0.1455680900968842</v>
       </c>
       <c r="T77">
-        <v>1.824111760226893</v>
+        <v>1.892563802547776</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.344040016560548</v>
+        <v>3.300039490026856</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.0687355024232522</v>
+        <v>0.068626674045355</v>
       </c>
       <c r="C78">
-        <v>927.7999102796646</v>
+        <v>917.332800017318</v>
       </c>
       <c r="D78">
-        <v>2154.117546594419</v>
+        <v>2164.387510494108</v>
       </c>
       <c r="E78">
-        <v>1140.71022011113</v>
+        <v>1161.447294273167</v>
       </c>
       <c r="F78">
-        <v>1576.017636314754</v>
+        <v>1596.75471047679</v>
       </c>
       <c r="G78">
         <v>349.7</v>
@@ -7683,28 +7683,28 @@
         <v>333.379</v>
       </c>
       <c r="M78">
-        <v>101.0227304877757</v>
+        <v>102.3519769415623</v>
       </c>
       <c r="N78">
-        <v>232.3562695122242</v>
+        <v>231.0270230584377</v>
       </c>
       <c r="O78">
-        <v>71.14748972464307</v>
+        <v>70.74047446049363</v>
       </c>
       <c r="P78">
-        <v>161.2087797875812</v>
+        <v>160.2865485979441</v>
       </c>
       <c r="Q78">
-        <v>161.5397797875812</v>
+        <v>160.6175485979441</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1455680900968842</v>
+        <v>0.1494903801971956</v>
       </c>
       <c r="T78">
-        <v>1.892563802547776</v>
+        <v>1.966968196374823</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.300039490026856</v>
+        <v>3.257181834312222</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.068626674045355</v>
+        <v>0.06851784566745778</v>
       </c>
       <c r="C79">
-        <v>917.332800017318</v>
+        <v>906.9640849574603</v>
       </c>
       <c r="D79">
-        <v>2164.387510494108</v>
+        <v>2174.755869596287</v>
       </c>
       <c r="E79">
-        <v>1161.447294273167</v>
+        <v>1182.184368435203</v>
       </c>
       <c r="F79">
-        <v>1596.75471047679</v>
+        <v>1617.491784638827</v>
       </c>
       <c r="G79">
         <v>349.7</v>
@@ -7765,28 +7765,28 @@
         <v>333.379</v>
       </c>
       <c r="M79">
-        <v>102.3519769415623</v>
+        <v>103.6812233953488</v>
       </c>
       <c r="N79">
-        <v>231.0270230584377</v>
+        <v>229.6977766046512</v>
       </c>
       <c r="O79">
-        <v>70.74047446049363</v>
+        <v>70.33345919634419</v>
       </c>
       <c r="P79">
-        <v>160.2865485979441</v>
+        <v>159.364317408307</v>
       </c>
       <c r="Q79">
-        <v>160.6175485979441</v>
+        <v>159.6953174083069</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1494903801971956</v>
+        <v>0.1537692421248081</v>
       </c>
       <c r="T79">
-        <v>1.966968196374823</v>
+        <v>2.048136626004329</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.257181834312222</v>
+        <v>3.21542309284668</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.06851784566745778</v>
+        <v>0.06840901728956056</v>
       </c>
       <c r="C80">
-        <v>906.9640849574603</v>
+        <v>896.6951859743558</v>
       </c>
       <c r="D80">
-        <v>2174.755869596287</v>
+        <v>2185.224044775219</v>
       </c>
       <c r="E80">
-        <v>1182.184368435203</v>
+        <v>1202.921442597239</v>
       </c>
       <c r="F80">
-        <v>1617.491784638827</v>
+        <v>1638.228858800863</v>
       </c>
       <c r="G80">
         <v>349.7</v>
@@ -7847,28 +7847,28 @@
         <v>333.379</v>
       </c>
       <c r="M80">
-        <v>103.6812233953488</v>
+        <v>105.0104698491353</v>
       </c>
       <c r="N80">
-        <v>229.6977766046512</v>
+        <v>228.3685301508647</v>
       </c>
       <c r="O80">
-        <v>70.33345919634419</v>
+        <v>69.92644393219477</v>
       </c>
       <c r="P80">
-        <v>159.364317408307</v>
+        <v>158.4420862186699</v>
       </c>
       <c r="Q80">
-        <v>159.6953174083069</v>
+        <v>158.7730862186699</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1537692421248081</v>
+        <v>0.1584556147121932</v>
       </c>
       <c r="T80">
-        <v>2.048136626004329</v>
+        <v>2.137035382265217</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.21542309284668</v>
+        <v>3.174721534709381</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.06840901728956056</v>
+        <v>0.06830018891166334</v>
       </c>
       <c r="C81">
-        <v>896.6951859743558</v>
+        <v>886.5275514320736</v>
       </c>
       <c r="D81">
-        <v>2185.224044775219</v>
+        <v>2195.793484394973</v>
       </c>
       <c r="E81">
-        <v>1202.921442597239</v>
+        <v>1223.658516759275</v>
       </c>
       <c r="F81">
-        <v>1638.228858800863</v>
+        <v>1658.965932962899</v>
       </c>
       <c r="G81">
         <v>349.7</v>
@@ -7929,28 +7929,28 @@
         <v>333.379</v>
       </c>
       <c r="M81">
-        <v>105.0104698491353</v>
+        <v>106.3397163029218</v>
       </c>
       <c r="N81">
-        <v>228.3685301508647</v>
+        <v>227.0392836970781</v>
       </c>
       <c r="O81">
-        <v>69.92644393219477</v>
+        <v>69.51942866804534</v>
       </c>
       <c r="P81">
-        <v>158.4420862186699</v>
+        <v>157.5198550290328</v>
       </c>
       <c r="Q81">
-        <v>158.7730862186699</v>
+        <v>157.8508550290328</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1584556147121932</v>
+        <v>0.1636106245583167</v>
       </c>
       <c r="T81">
-        <v>2.137035382265217</v>
+        <v>2.234824014152193</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.174721534709381</v>
+        <v>3.135037515525513</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.06830018891166334</v>
+        <v>0.06819136053376612</v>
       </c>
       <c r="C82">
-        <v>886.5275514320736</v>
+        <v>876.4626578525269</v>
       </c>
       <c r="D82">
-        <v>2195.793484394973</v>
+        <v>2206.465664977462</v>
       </c>
       <c r="E82">
-        <v>1223.658516759275</v>
+        <v>1244.395590921312</v>
       </c>
       <c r="F82">
-        <v>1658.965932962899</v>
+        <v>1679.703007124935</v>
       </c>
       <c r="G82">
         <v>349.7</v>
@@ -8011,28 +8011,28 @@
         <v>333.379</v>
       </c>
       <c r="M82">
-        <v>106.3397163029218</v>
+        <v>107.6689627567084</v>
       </c>
       <c r="N82">
-        <v>227.0392836970781</v>
+        <v>225.7100372432916</v>
       </c>
       <c r="O82">
-        <v>69.51942866804534</v>
+        <v>69.11241340389589</v>
       </c>
       <c r="P82">
-        <v>157.5198550290328</v>
+        <v>156.5976238393957</v>
       </c>
       <c r="Q82">
-        <v>157.8508550290328</v>
+        <v>156.9286238393957</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1636106245583167</v>
+        <v>0.1693082670198218</v>
       </c>
       <c r="T82">
-        <v>2.234824014152193</v>
+        <v>2.342906186237798</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.135037515525513</v>
+        <v>3.096333348667173</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.06819136053376612</v>
+        <v>0.0680825321558689</v>
       </c>
       <c r="C83">
-        <v>876.4626578525269</v>
+        <v>866.502010603092</v>
       </c>
       <c r="D83">
-        <v>2206.465664977462</v>
+        <v>2217.242091890064</v>
       </c>
       <c r="E83">
-        <v>1244.395590921312</v>
+        <v>1265.132665083348</v>
       </c>
       <c r="F83">
-        <v>1679.703007124935</v>
+        <v>1700.440081286972</v>
       </c>
       <c r="G83">
         <v>349.7</v>
@@ -8093,28 +8093,28 @@
         <v>333.379</v>
       </c>
       <c r="M83">
-        <v>107.6689627567084</v>
+        <v>108.9982092104949</v>
       </c>
       <c r="N83">
-        <v>225.7100372432916</v>
+        <v>224.3807907895051</v>
       </c>
       <c r="O83">
-        <v>69.11241340389589</v>
+        <v>68.70539813974645</v>
       </c>
       <c r="P83">
-        <v>156.5976238393957</v>
+        <v>155.6753926497586</v>
       </c>
       <c r="Q83">
-        <v>156.9286238393957</v>
+        <v>156.0063926497586</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1693082670198218</v>
+        <v>0.1756389808659385</v>
       </c>
       <c r="T83">
-        <v>2.342906186237798</v>
+        <v>2.462997488555137</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.096333348667173</v>
+        <v>3.058573185878549</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.0680825321558689</v>
+        <v>0.0679737037779717</v>
       </c>
       <c r="C84">
-        <v>866.502010603092</v>
+        <v>856.6471446044711</v>
       </c>
       <c r="D84">
-        <v>2217.242091890064</v>
+        <v>2228.124300053479</v>
       </c>
       <c r="E84">
-        <v>1265.132665083348</v>
+        <v>1285.869739245384</v>
       </c>
       <c r="F84">
-        <v>1700.440081286972</v>
+        <v>1721.177155449008</v>
       </c>
       <c r="G84">
         <v>349.7</v>
@@ -8175,28 +8175,28 @@
         <v>333.379</v>
       </c>
       <c r="M84">
-        <v>108.9982092104949</v>
+        <v>110.3274556642814</v>
       </c>
       <c r="N84">
-        <v>224.3807907895051</v>
+        <v>223.0515443357185</v>
       </c>
       <c r="O84">
-        <v>68.70539813974645</v>
+        <v>68.29838287559703</v>
       </c>
       <c r="P84">
-        <v>155.6753926497586</v>
+        <v>154.7531614601215</v>
       </c>
       <c r="Q84">
-        <v>156.0063926497586</v>
+        <v>155.0841614601215</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1756389808659385</v>
+        <v>0.1827144845763042</v>
       </c>
       <c r="T84">
-        <v>2.462997488555137</v>
+        <v>2.597217179380399</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.058573185878549</v>
+        <v>3.021722906530615</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.0679737037779717</v>
+        <v>0.07241065300007449</v>
       </c>
       <c r="C85">
-        <v>856.6471446044711</v>
+        <v>464.4019236922243</v>
       </c>
       <c r="D85">
-        <v>2228.124300053479</v>
+        <v>1856.616153303269</v>
       </c>
       <c r="E85">
-        <v>1285.869739245384</v>
+        <v>1306.606813407421</v>
       </c>
       <c r="F85">
-        <v>1721.177155449008</v>
+        <v>1741.914229611044</v>
       </c>
       <c r="G85">
         <v>349.7</v>
@@ -8257,45 +8257,45 @@
         <v>333.379</v>
       </c>
       <c r="M85">
-        <v>110.3274556642814</v>
+        <v>125.2436331090341</v>
       </c>
       <c r="N85">
-        <v>223.0515443357185</v>
+        <v>208.1353668909659</v>
       </c>
       <c r="O85">
-        <v>68.29838287559703</v>
+        <v>63.73104934201376</v>
       </c>
       <c r="P85">
-        <v>154.7531614601215</v>
+        <v>144.4043175489521</v>
       </c>
       <c r="Q85">
-        <v>155.0841614601215</v>
+        <v>144.7353175489521</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1827144845763042</v>
+        <v>0.1906744262504656</v>
       </c>
       <c r="T85">
-        <v>2.597217179380399</v>
+        <v>2.748214331558818</v>
       </c>
       <c r="U85">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V85">
         <v>0.3062</v>
       </c>
       <c r="W85">
-        <v>0.04447258</v>
+        <v>0.04988422</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y85">
-        <v>3.021722906530615</v>
+        <v>2.661843893571566</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07241065300007449</v>
+        <v>0.07235594102217727</v>
       </c>
       <c r="C86">
-        <v>464.4019236922245</v>
+        <v>447.4899499797757</v>
       </c>
       <c r="D86">
-        <v>1856.616153303269</v>
+        <v>1860.441253752856</v>
       </c>
       <c r="E86">
-        <v>1306.60681340742</v>
+        <v>1327.343887569456</v>
       </c>
       <c r="F86">
-        <v>1741.914229611044</v>
+        <v>1762.65130377308</v>
       </c>
       <c r="G86">
         <v>349.7</v>
@@ -8339,28 +8339,28 @@
         <v>333.379</v>
       </c>
       <c r="M86">
-        <v>125.2436331090341</v>
+        <v>126.7346287412845</v>
       </c>
       <c r="N86">
-        <v>208.1353668909659</v>
+        <v>206.6443712587155</v>
       </c>
       <c r="O86">
-        <v>63.73104934201376</v>
+        <v>63.27450647941869</v>
       </c>
       <c r="P86">
-        <v>144.4043175489521</v>
+        <v>143.3698647792968</v>
       </c>
       <c r="Q86">
-        <v>144.7353175489521</v>
+        <v>143.7008647792968</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1906744262504655</v>
+        <v>0.1996956934811818</v>
       </c>
       <c r="T86">
-        <v>2.748214331558817</v>
+        <v>2.919344437361025</v>
       </c>
       <c r="U86">
         <v>0.07190000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.661843893571566</v>
+        <v>2.63052808305896</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07235594102217727</v>
+        <v>0.07230122904428005</v>
       </c>
       <c r="C87">
-        <v>447.4899499797757</v>
+        <v>430.5937701620862</v>
       </c>
       <c r="D87">
-        <v>1860.441253752856</v>
+        <v>1864.282148097203</v>
       </c>
       <c r="E87">
-        <v>1327.343887569456</v>
+        <v>1348.080961731493</v>
       </c>
       <c r="F87">
-        <v>1762.65130377308</v>
+        <v>1783.388377935117</v>
       </c>
       <c r="G87">
         <v>349.7</v>
@@ -8421,28 +8421,28 @@
         <v>333.379</v>
       </c>
       <c r="M87">
-        <v>126.7346287412845</v>
+        <v>128.2256243735349</v>
       </c>
       <c r="N87">
-        <v>206.6443712587155</v>
+        <v>205.1533756264651</v>
       </c>
       <c r="O87">
-        <v>63.27450647941869</v>
+        <v>62.81796361682361</v>
       </c>
       <c r="P87">
-        <v>143.3698647792968</v>
+        <v>142.3354120096415</v>
       </c>
       <c r="Q87">
-        <v>143.7008647792968</v>
+        <v>142.6664120096414</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1996956934811818</v>
+        <v>0.2100057131734289</v>
       </c>
       <c r="T87">
-        <v>2.919344437361025</v>
+        <v>3.114921701134977</v>
       </c>
       <c r="U87">
         <v>0.07190000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.63052808305896</v>
+        <v>2.599940547209437</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07230122904428005</v>
+        <v>0.07224651706638284</v>
       </c>
       <c r="C88">
-        <v>430.5937701620862</v>
+        <v>413.7134822613496</v>
       </c>
       <c r="D88">
-        <v>1864.282148097203</v>
+        <v>1868.138934358502</v>
       </c>
       <c r="E88">
-        <v>1348.080961731493</v>
+        <v>1368.818035893529</v>
       </c>
       <c r="F88">
-        <v>1783.388377935117</v>
+        <v>1804.125452097153</v>
       </c>
       <c r="G88">
         <v>349.7</v>
@@ -8503,28 +8503,28 @@
         <v>333.379</v>
       </c>
       <c r="M88">
-        <v>128.2256243735349</v>
+        <v>129.7166200057853</v>
       </c>
       <c r="N88">
-        <v>205.1533756264651</v>
+        <v>203.6623799942147</v>
       </c>
       <c r="O88">
-        <v>62.81796361682361</v>
+        <v>62.36142075422854</v>
       </c>
       <c r="P88">
-        <v>142.3354120096415</v>
+        <v>141.3009592399862</v>
       </c>
       <c r="Q88">
-        <v>142.6664120096414</v>
+        <v>141.6319592399861</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2100057131734289</v>
+        <v>0.2219018897414064</v>
       </c>
       <c r="T88">
-        <v>3.114921701134977</v>
+        <v>3.340587774720306</v>
       </c>
       <c r="U88">
         <v>0.07190000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.599940547209437</v>
+        <v>2.570056173103581</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07224651706638284</v>
+        <v>0.07219180508848563</v>
       </c>
       <c r="C89">
-        <v>413.7134822613496</v>
+        <v>396.8491851125889</v>
       </c>
       <c r="D89">
-        <v>1868.138934358502</v>
+        <v>1872.011711371778</v>
       </c>
       <c r="E89">
-        <v>1368.818035893529</v>
+        <v>1389.555110055565</v>
       </c>
       <c r="F89">
-        <v>1804.125452097153</v>
+        <v>1824.862526259189</v>
       </c>
       <c r="G89">
         <v>349.7</v>
@@ -8585,28 +8585,28 @@
         <v>333.379</v>
       </c>
       <c r="M89">
-        <v>129.7166200057853</v>
+        <v>131.2076156380357</v>
       </c>
       <c r="N89">
-        <v>203.6623799942147</v>
+        <v>202.1713843619643</v>
       </c>
       <c r="O89">
-        <v>62.36142075422854</v>
+        <v>61.90487789163347</v>
       </c>
       <c r="P89">
-        <v>141.3009592399862</v>
+        <v>140.2665064703308</v>
       </c>
       <c r="Q89">
-        <v>141.6319592399861</v>
+        <v>140.5975064703308</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2219018897414064</v>
+        <v>0.2357807624040469</v>
       </c>
       <c r="T89">
-        <v>3.340587774720306</v>
+        <v>3.603864860569858</v>
       </c>
       <c r="U89">
         <v>0.07190000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.570056173103581</v>
+        <v>2.540850989318313</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07219180508848563</v>
+        <v>0.07213709311058841</v>
       </c>
       <c r="C90">
-        <v>396.8491851125889</v>
+        <v>380.0009783720952</v>
       </c>
       <c r="D90">
-        <v>1872.011711371778</v>
+        <v>1875.90057879332</v>
       </c>
       <c r="E90">
-        <v>1389.555110055565</v>
+        <v>1410.292184217602</v>
       </c>
       <c r="F90">
-        <v>1824.862526259189</v>
+        <v>1845.599600421225</v>
       </c>
       <c r="G90">
         <v>349.7</v>
@@ -8667,28 +8667,28 @@
         <v>333.379</v>
       </c>
       <c r="M90">
-        <v>131.2076156380357</v>
+        <v>132.6986112702861</v>
       </c>
       <c r="N90">
-        <v>202.1713843619643</v>
+        <v>200.6803887297139</v>
       </c>
       <c r="O90">
-        <v>61.90487789163347</v>
+        <v>61.44833502903839</v>
       </c>
       <c r="P90">
-        <v>140.2665064703308</v>
+        <v>139.2320537006755</v>
       </c>
       <c r="Q90">
-        <v>140.5975064703308</v>
+        <v>139.5630537006755</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2357807624040469</v>
+        <v>0.2521830664598946</v>
       </c>
       <c r="T90">
-        <v>3.603864860569858</v>
+        <v>3.915010507482964</v>
       </c>
       <c r="U90">
         <v>0.07190000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.540850989318313</v>
+        <v>2.512302101797882</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07213709311058841</v>
+        <v>0.0745176191326912</v>
       </c>
       <c r="C91">
-        <v>380.0009783720952</v>
+        <v>203.7624985377606</v>
       </c>
       <c r="D91">
-        <v>1875.90057879332</v>
+        <v>1720.399173121022</v>
       </c>
       <c r="E91">
-        <v>1410.292184217602</v>
+        <v>1431.029258379638</v>
       </c>
       <c r="F91">
-        <v>1845.599600421225</v>
+        <v>1866.336674583261</v>
       </c>
       <c r="G91">
         <v>349.7</v>
@@ -8749,45 +8749,45 @@
         <v>333.379</v>
       </c>
       <c r="M91">
-        <v>132.6986112702861</v>
+        <v>141.4683199334112</v>
       </c>
       <c r="N91">
-        <v>200.6803887297139</v>
+        <v>191.9106800665888</v>
       </c>
       <c r="O91">
-        <v>61.44833502903839</v>
+        <v>58.76305023638948</v>
       </c>
       <c r="P91">
-        <v>139.2320537006755</v>
+        <v>133.1476298301993</v>
       </c>
       <c r="Q91">
-        <v>139.5630537006755</v>
+        <v>133.4786298301993</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2521830664598946</v>
+        <v>0.2718658313269119</v>
       </c>
       <c r="T91">
-        <v>3.915010507482964</v>
+        <v>4.288385283778691</v>
       </c>
       <c r="U91">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V91">
         <v>0.3062</v>
       </c>
       <c r="W91">
-        <v>0.04988422</v>
+        <v>0.05259004</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y91">
-        <v>2.512302101797882</v>
+        <v>2.356562940430201</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.0745176191326912</v>
+        <v>0.07448996535479399</v>
       </c>
       <c r="C92">
-        <v>203.7624985377606</v>
+        <v>184.6836883728981</v>
       </c>
       <c r="D92">
-        <v>1720.399173121022</v>
+        <v>1722.057437118196</v>
       </c>
       <c r="E92">
-        <v>1431.029258379638</v>
+        <v>1451.766332541674</v>
       </c>
       <c r="F92">
-        <v>1866.336674583261</v>
+        <v>1887.073748745298</v>
       </c>
       <c r="G92">
         <v>349.7</v>
@@ -8831,28 +8831,28 @@
         <v>333.379</v>
       </c>
       <c r="M92">
-        <v>141.4683199334112</v>
+        <v>143.0401901548936</v>
       </c>
       <c r="N92">
-        <v>191.9106800665888</v>
+        <v>190.3388098451064</v>
       </c>
       <c r="O92">
-        <v>58.76305023638948</v>
+        <v>58.28174357457158</v>
       </c>
       <c r="P92">
-        <v>133.1476298301993</v>
+        <v>132.0570662705348</v>
       </c>
       <c r="Q92">
-        <v>133.4786298301993</v>
+        <v>132.3880662705348</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2718658313269119</v>
+        <v>0.2959225439421554</v>
       </c>
       <c r="T92">
-        <v>4.288385283778691</v>
+        <v>4.74473223258458</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.356562940430201</v>
+        <v>2.330666644381517</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.07448996535479399</v>
+        <v>0.07446231157689677</v>
       </c>
       <c r="C93">
-        <v>184.6836883728981</v>
+        <v>165.6080780381801</v>
       </c>
       <c r="D93">
-        <v>1722.057437118196</v>
+        <v>1723.718900945514</v>
       </c>
       <c r="E93">
-        <v>1451.766332541674</v>
+        <v>1472.50340670371</v>
       </c>
       <c r="F93">
-        <v>1887.073748745298</v>
+        <v>1907.810822907334</v>
       </c>
       <c r="G93">
         <v>349.7</v>
@@ -8913,28 +8913,28 @@
         <v>333.379</v>
       </c>
       <c r="M93">
-        <v>143.0401901548936</v>
+        <v>144.6120603763759</v>
       </c>
       <c r="N93">
-        <v>190.3388098451064</v>
+        <v>188.766939623624</v>
       </c>
       <c r="O93">
-        <v>58.28174357457158</v>
+        <v>57.80043691275369</v>
       </c>
       <c r="P93">
-        <v>132.0570662705348</v>
+        <v>130.9665027108703</v>
       </c>
       <c r="Q93">
-        <v>132.3880662705348</v>
+        <v>131.2975027108703</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2959225439421554</v>
+        <v>0.3259934347112097</v>
       </c>
       <c r="T93">
-        <v>4.74473223258458</v>
+        <v>5.315165918591942</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.330666644381517</v>
+        <v>2.305333311290414</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.07446231157689677</v>
+        <v>0.07443465779899955</v>
       </c>
       <c r="C94">
-        <v>165.6080780381801</v>
+        <v>146.5356768042643</v>
       </c>
       <c r="D94">
-        <v>1723.718900945514</v>
+        <v>1725.383573873635</v>
       </c>
       <c r="E94">
-        <v>1472.50340670371</v>
+        <v>1493.240480865747</v>
       </c>
       <c r="F94">
-        <v>1907.810822907334</v>
+        <v>1928.54789706937</v>
       </c>
       <c r="G94">
         <v>349.7</v>
@@ -8995,28 +8995,28 @@
         <v>333.379</v>
       </c>
       <c r="M94">
-        <v>144.6120603763759</v>
+        <v>146.1839305978583</v>
       </c>
       <c r="N94">
-        <v>188.766939623624</v>
+        <v>187.1950694021417</v>
       </c>
       <c r="O94">
-        <v>57.80043691275369</v>
+        <v>57.31913025093579</v>
       </c>
       <c r="P94">
-        <v>130.9665027108703</v>
+        <v>129.8759391512059</v>
       </c>
       <c r="Q94">
-        <v>131.2975027108703</v>
+        <v>130.2069391512059</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3259934347112097</v>
+        <v>0.3646560085571366</v>
       </c>
       <c r="T94">
-        <v>5.315165918591942</v>
+        <v>6.048580657744265</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.305333311290414</v>
+        <v>2.280544781061485</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.07443465779899955</v>
+        <v>0.07440700402110234</v>
       </c>
       <c r="C95">
-        <v>146.5356768042643</v>
+        <v>127.4664939776571</v>
       </c>
       <c r="D95">
-        <v>1725.383573873635</v>
+        <v>1727.051465209064</v>
       </c>
       <c r="E95">
-        <v>1493.240480865747</v>
+        <v>1513.977555027783</v>
       </c>
       <c r="F95">
-        <v>1928.54789706937</v>
+        <v>1949.284971231406</v>
       </c>
       <c r="G95">
         <v>349.7</v>
@@ -9077,28 +9077,28 @@
         <v>333.379</v>
       </c>
       <c r="M95">
-        <v>146.1839305978583</v>
+        <v>147.7558008193406</v>
       </c>
       <c r="N95">
-        <v>187.1950694021417</v>
+        <v>185.6231991806594</v>
       </c>
       <c r="O95">
-        <v>57.31913025093579</v>
+        <v>56.8378235891179</v>
       </c>
       <c r="P95">
-        <v>129.8759391512059</v>
+        <v>128.7853755915415</v>
       </c>
       <c r="Q95">
-        <v>130.2069391512059</v>
+        <v>129.1163755915414</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3646560085571366</v>
+        <v>0.4162061070183726</v>
       </c>
       <c r="T95">
-        <v>6.048580657744265</v>
+        <v>7.026466976614028</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.280544781061485</v>
+        <v>2.256283666369341</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07440700402110234</v>
+        <v>0.07437935024320512</v>
       </c>
       <c r="C96">
-        <v>127.4664939776571</v>
+        <v>108.4005389008883</v>
       </c>
       <c r="D96">
-        <v>1727.051465209064</v>
+        <v>1728.722584294331</v>
       </c>
       <c r="E96">
-        <v>1513.977555027783</v>
+        <v>1534.714629189819</v>
       </c>
       <c r="F96">
-        <v>1949.284971231406</v>
+        <v>1970.022045393443</v>
       </c>
       <c r="G96">
         <v>349.7</v>
@@ -9159,28 +9159,28 @@
         <v>333.379</v>
       </c>
       <c r="M96">
-        <v>147.7558008193406</v>
+        <v>149.327671040823</v>
       </c>
       <c r="N96">
-        <v>185.6231991806594</v>
+        <v>184.051328959177</v>
       </c>
       <c r="O96">
-        <v>56.8378235891179</v>
+        <v>56.3565169273</v>
       </c>
       <c r="P96">
-        <v>128.7853755915415</v>
+        <v>127.694812031877</v>
       </c>
       <c r="Q96">
-        <v>129.1163755915414</v>
+        <v>128.025812031877</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4162061070183726</v>
+        <v>0.488376244864103</v>
       </c>
       <c r="T96">
-        <v>7.026466976614028</v>
+        <v>8.395507823031698</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.256283666369341</v>
+        <v>2.232533311986506</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07437935024320512</v>
+        <v>0.0743516964653079</v>
       </c>
       <c r="C97">
-        <v>108.4005389008883</v>
+        <v>89.33782095267929</v>
       </c>
       <c r="D97">
-        <v>1728.722584294331</v>
+        <v>1730.396940508158</v>
       </c>
       <c r="E97">
-        <v>1534.714629189819</v>
+        <v>1555.451703351855</v>
       </c>
       <c r="F97">
-        <v>1970.022045393443</v>
+        <v>1990.759119555479</v>
       </c>
       <c r="G97">
         <v>349.7</v>
@@ -9241,28 +9241,28 @@
         <v>333.379</v>
       </c>
       <c r="M97">
-        <v>149.327671040823</v>
+        <v>150.8995412623053</v>
       </c>
       <c r="N97">
-        <v>184.051328959177</v>
+        <v>182.4794587376946</v>
       </c>
       <c r="O97">
-        <v>56.3565169273</v>
+        <v>55.8752102654821</v>
       </c>
       <c r="P97">
-        <v>127.694812031877</v>
+        <v>126.6042484722125</v>
       </c>
       <c r="Q97">
-        <v>128.025812031877</v>
+        <v>126.9352484722125</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.488376244864103</v>
+        <v>0.5966314516326986</v>
       </c>
       <c r="T97">
-        <v>8.395507823031698</v>
+        <v>10.4490690926582</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.232533311986506</v>
+        <v>2.209277756653313</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.07435169646530791</v>
+        <v>0.07432404268741069</v>
       </c>
       <c r="C98">
-        <v>89.33782095267816</v>
+        <v>70.27834954812101</v>
       </c>
       <c r="D98">
-        <v>1730.396940508157</v>
+        <v>1732.074543265636</v>
       </c>
       <c r="E98">
-        <v>1555.451703351855</v>
+        <v>1576.188777513891</v>
       </c>
       <c r="F98">
-        <v>1990.759119555479</v>
+        <v>2011.496193717515</v>
       </c>
       <c r="G98">
         <v>349.7</v>
@@ -9323,28 +9323,28 @@
         <v>333.379</v>
       </c>
       <c r="M98">
-        <v>150.8995412623053</v>
+        <v>152.4714114837876</v>
       </c>
       <c r="N98">
-        <v>182.4794587376947</v>
+        <v>180.9075885162123</v>
       </c>
       <c r="O98">
-        <v>55.87521026548211</v>
+        <v>55.39390360366421</v>
       </c>
       <c r="P98">
-        <v>126.6042484722126</v>
+        <v>125.5136849125481</v>
       </c>
       <c r="Q98">
-        <v>126.9352484722126</v>
+        <v>125.8446849125481</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5966314516326972</v>
+        <v>0.7770567962470224</v>
       </c>
       <c r="T98">
-        <v>10.44906909265818</v>
+        <v>13.87167120870234</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.209277756653313</v>
+        <v>2.186501697306372</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.07432404268741069</v>
+        <v>0.07429638890951348</v>
       </c>
       <c r="C99">
-        <v>70.27834954812101</v>
+        <v>51.22213413885424</v>
       </c>
       <c r="D99">
-        <v>1732.074543265636</v>
+        <v>1733.755402018406</v>
       </c>
       <c r="E99">
-        <v>1576.188777513891</v>
+        <v>1596.925851675928</v>
       </c>
       <c r="F99">
-        <v>2011.496193717515</v>
+        <v>2032.233267879551</v>
       </c>
       <c r="G99">
         <v>349.7</v>
@@ -9405,28 +9405,28 @@
         <v>333.379</v>
       </c>
       <c r="M99">
-        <v>152.4714114837876</v>
+        <v>154.04328170527</v>
       </c>
       <c r="N99">
-        <v>180.9075885162123</v>
+        <v>179.33571829473</v>
       </c>
       <c r="O99">
-        <v>55.39390360366421</v>
+        <v>54.91259694184632</v>
       </c>
       <c r="P99">
-        <v>125.5136849125481</v>
+        <v>124.4231213528836</v>
       </c>
       <c r="Q99">
-        <v>125.8446849125481</v>
+        <v>124.7541213528836</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7770567962470224</v>
+        <v>1.137907485475673</v>
       </c>
       <c r="T99">
-        <v>13.87167120870234</v>
+        <v>20.71687544079066</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.186501697306372</v>
+        <v>2.164190455497123</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.07429638890951348</v>
+        <v>0.07426873513161626</v>
       </c>
       <c r="C100">
-        <v>51.22213413885424</v>
+        <v>32.16918421324272</v>
       </c>
       <c r="D100">
-        <v>1733.755402018406</v>
+        <v>1735.439526254831</v>
       </c>
       <c r="E100">
-        <v>1596.925851675928</v>
+        <v>1617.662925837964</v>
       </c>
       <c r="F100">
-        <v>2032.233267879551</v>
+        <v>2052.970342041588</v>
       </c>
       <c r="G100">
         <v>349.7</v>
@@ -9487,28 +9487,28 @@
         <v>333.379</v>
       </c>
       <c r="M100">
-        <v>154.04328170527</v>
+        <v>155.6151519267524</v>
       </c>
       <c r="N100">
-        <v>179.33571829473</v>
+        <v>177.7638480732476</v>
       </c>
       <c r="O100">
-        <v>54.91259694184632</v>
+        <v>54.43129028002842</v>
       </c>
       <c r="P100">
-        <v>124.4231213528836</v>
+        <v>123.3325577932192</v>
       </c>
       <c r="Q100">
-        <v>124.7541213528836</v>
+        <v>123.6635577932192</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.137907485475673</v>
+        <v>2.220459553161624</v>
       </c>
       <c r="T100">
-        <v>20.71687544079066</v>
+        <v>41.25248813705562</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.164190455497123</v>
+        <v>2.142329945845637</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.07426873513161626</v>
-      </c>
-      <c r="C101">
-        <v>32.16918421324272</v>
-      </c>
-      <c r="D101">
-        <v>1735.439526254831</v>
-      </c>
-      <c r="E101">
-        <v>1617.662925837964</v>
-      </c>
-      <c r="F101">
-        <v>2052.970342041588</v>
-      </c>
-      <c r="G101">
-        <v>349.7</v>
-      </c>
-      <c r="H101">
-        <v>1638.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>333.71</v>
-      </c>
-      <c r="K101">
-        <v>0.331</v>
-      </c>
-      <c r="L101">
-        <v>333.379</v>
-      </c>
-      <c r="M101">
-        <v>155.6151519267524</v>
-      </c>
-      <c r="N101">
-        <v>177.7638480732476</v>
-      </c>
-      <c r="O101">
-        <v>54.43129028002842</v>
-      </c>
-      <c r="P101">
-        <v>123.3325577932192</v>
-      </c>
-      <c r="Q101">
-        <v>123.6635577932192</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.220459553161624</v>
-      </c>
-      <c r="T101">
-        <v>41.25248813705562</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.3062</v>
-      </c>
-      <c r="W101">
-        <v>0.05259004</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.142329945845637</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
